--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C138"/>
+  <dimension ref="A1:C137"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -420,7 +420,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>பூபதி இபி</v>
+        <v>Santhosh R</v>
       </c>
       <c r="C2">
         <v>1000</v>
@@ -431,7 +431,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Santhosh R</v>
+        <v>Suresh</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -442,10 +442,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Suresh</v>
+        <v>ஸ்ரீனிவாச அய்யர்</v>
       </c>
       <c r="C4">
-        <v>1000</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="5">
@@ -453,10 +453,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>ஸ்ரீனிவாச அய்யர்</v>
+        <v>லட்சுமி</v>
       </c>
       <c r="C5">
-        <v>10001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="6">
@@ -464,10 +464,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>லட்சுமி</v>
+        <v>செந்தில் (சக்கரவர்த்தி)</v>
       </c>
       <c r="C6">
-        <v>5001</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="7">
@@ -475,10 +475,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>செந்தில் (சக்கரவர்த்தி)</v>
+        <v>ஆனந்த்</v>
       </c>
       <c r="C7">
-        <v>4700</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="8">
@@ -486,7 +486,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>ஆனந்த்</v>
+        <v>யோகேஷ்</v>
       </c>
       <c r="C8">
         <v>19000</v>
@@ -497,10 +497,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>யோகேஷ்</v>
+        <v>சுரேஷ்</v>
       </c>
       <c r="C9">
-        <v>19000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="10">
@@ -508,10 +508,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>சுரேஷ்</v>
+        <v>பூபதி</v>
       </c>
       <c r="C10">
-        <v>20000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="11">
@@ -519,10 +519,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>பூபதி</v>
+        <v>நந்தகுமார்</v>
       </c>
       <c r="C11">
-        <v>27500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="12">
@@ -530,10 +530,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>நந்தகுமார்</v>
+        <v>ரமேஷ்(டிரைவர்)</v>
       </c>
       <c r="C12">
-        <v>9500</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -541,10 +541,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>ரமேஷ்(டிரைவர்)</v>
+        <v>கண்ணன்(post)</v>
       </c>
       <c r="C13">
-        <v>101</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="14">
@@ -552,10 +552,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>கண்ணன்(post)</v>
+        <v>ரமேஷ்(PC)</v>
       </c>
       <c r="C14">
-        <v>10001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15">
@@ -563,10 +563,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>ரமேஷ்(PC)</v>
+        <v>வெற்றிவேல்</v>
       </c>
       <c r="C15">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="16">
@@ -574,7 +574,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>வெற்றிவேல்</v>
+        <v>ஏ. தினேஷ்குமார்</v>
       </c>
       <c r="C16">
         <v>3000</v>
@@ -585,10 +585,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>ஏ. தினேஷ்குமார்</v>
+        <v>சூர்யா கார்த்தி (சீலைபில்லையர்புதூர்)</v>
       </c>
       <c r="C17">
-        <v>3000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="18">
@@ -596,10 +596,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>சூர்யா கார்த்தி (சீலைபில்லையர்புதூர்)</v>
+        <v>சுஜிதா ஈரோடு</v>
       </c>
       <c r="C18">
-        <v>12000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="19">
@@ -607,10 +607,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>சுஜிதா ஈரோடு</v>
+        <v>நாகராஜ் அய்யர்</v>
       </c>
       <c r="C19">
-        <v>2000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20">
@@ -618,10 +618,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>நாகராஜ் அய்யர்</v>
+        <v>நட்ராஜ் கோவை (மணி)</v>
       </c>
       <c r="C20">
-        <v>500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="21">
@@ -629,10 +629,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>நட்ராஜ் கோவை (மணி)</v>
+        <v>தனலட்சுமி புகழேந்தி</v>
       </c>
       <c r="C21">
-        <v>5500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22">
@@ -640,10 +640,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>தனலட்சுமி புகழேந்தி</v>
+        <v>ராஜசேகர் பழனியப்பன்</v>
       </c>
       <c r="C22">
-        <v>500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>ராஜசேகர் பழனியப்பன்</v>
+        <v>நடராஜன் சைக்கிள்</v>
       </c>
       <c r="C23">
-        <v>10000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="24">
@@ -662,10 +662,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>நடராஜன் சைக்கிள்</v>
+        <v>எவுரி (postal)</v>
       </c>
       <c r="C24">
-        <v>1000</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="25">
@@ -673,10 +673,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>எவுரி (postal)</v>
+        <v>அருண் இரத்த பரிசோதனை (காட்டுபுத்தூர்)</v>
       </c>
       <c r="C25">
-        <v>5001</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="26">
@@ -684,10 +684,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>அருண் இரத்த பரிசோதனை (காட்டுபுத்தூர்)</v>
+        <v>ராஜேந்திரன் சுப்ரமணி</v>
       </c>
       <c r="C26">
-        <v>15000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="27">
@@ -695,10 +695,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>ராஜேந்திரன் சுப்ரமணி</v>
+        <v>சந்தோஸ் ரமேஷ்</v>
       </c>
       <c r="C27">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="28">
@@ -706,10 +706,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>சந்தோஸ் ரமேஷ்</v>
+        <v>ரமேஷ் பன்னீர்செல்வம்</v>
       </c>
       <c r="C28">
-        <v>10000</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="29">
@@ -717,10 +717,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>ரமேஷ் பன்னீர்செல்வம்</v>
+        <v>முத்துகிருஷ்ணன்</v>
       </c>
       <c r="C29">
-        <v>10001</v>
+        <v>5501</v>
       </c>
     </row>
     <row r="30">
@@ -728,10 +728,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>முத்துகிருஷ்ணன்</v>
+        <v>சுபாஷினி காட்டுப்புத்தூர்</v>
       </c>
       <c r="C30">
-        <v>5501</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="31">
@@ -739,10 +739,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>சுபாஷினி காட்டுப்புத்தூர்</v>
+        <v>அமுதா அன்பாநந்தன்</v>
       </c>
       <c r="C31">
-        <v>1000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="32">
@@ -750,10 +750,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>அமுதா அன்பாநந்தன்</v>
+        <v>கமல்நாத் கொளக்குடி</v>
       </c>
       <c r="C32">
-        <v>12500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33">
@@ -761,10 +761,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>கமல்நாத் கொளக்குடி</v>
+        <v>ஸ்ரீனிவாசபிரபு</v>
       </c>
       <c r="C33">
-        <v>300</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="34">
@@ -772,10 +772,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>ஸ்ரீனிவாசபிரபு</v>
+        <v>நாகவேல்</v>
       </c>
       <c r="C34">
-        <v>5001</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="35">
@@ -783,10 +783,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>நாகவேல்</v>
+        <v>செல்வராஜ் (TNEB)</v>
       </c>
       <c r="C35">
-        <v>17500</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="36">
@@ -794,7 +794,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>செல்வராஜ் (TNEB)</v>
+        <v>சதிஸ்குமார் (VAO)</v>
       </c>
       <c r="C36">
         <v>10001</v>
@@ -805,10 +805,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>சதிஸ்குமார் (VAO)</v>
+        <v>சரவணன் சதாசிவம்</v>
       </c>
       <c r="C37">
-        <v>10001</v>
+        <v>10501</v>
       </c>
     </row>
     <row r="38">
@@ -816,10 +816,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>சரவணன் சதாசிவம்</v>
+        <v>பிரியா நரேந்தரகுமார்</v>
       </c>
       <c r="C38">
-        <v>10501</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="39">
@@ -827,10 +827,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>பிரியா நரேந்தரகுமார்</v>
+        <v>புகழேந்தி டைலர்</v>
       </c>
       <c r="C39">
-        <v>1001</v>
+        <v>700</v>
       </c>
     </row>
     <row r="40">
@@ -838,10 +838,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>புகழேந்தி டைலர்</v>
+        <v>தங்கராசு கிருஷ்ணன்</v>
       </c>
       <c r="C40">
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="41">
@@ -849,10 +849,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>தங்கராசு கிருஷ்ணன்</v>
+        <v>சரவணன் ராஜசுந்தரி (தொட்டியம்)</v>
       </c>
       <c r="C41">
-        <v>2000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="42">
@@ -860,10 +860,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>சரவணன் ராஜசுந்தரி (தொட்டியம்)</v>
+        <v>ரெங்கநாதன் ரைஸ் மில்</v>
       </c>
       <c r="C42">
-        <v>10000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="43">
@@ -871,10 +871,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>ரெங்கநாதன் ரைஸ் மில்</v>
+        <v>வினோத் நீலமேகம்</v>
       </c>
       <c r="C43">
-        <v>25000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="44">
@@ -882,10 +882,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>வினோத் நீலமேகம்</v>
+        <v>சூர்யகுமார்</v>
       </c>
       <c r="C44">
-        <v>1000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="45">
@@ -893,10 +893,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>சூர்யகுமார்</v>
+        <v>சிவஞானம் ரெத்தினவேல்</v>
       </c>
       <c r="C45">
-        <v>2500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="46">
@@ -904,7 +904,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>சிவஞானம் ரெத்தினவேல்</v>
+        <v>நடராஜன் வாத்தியார்</v>
       </c>
       <c r="C46">
         <v>5000</v>
@@ -915,10 +915,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>நடராஜன் வாத்தியார்</v>
+        <v>பொங்கல் விளையாட்டு பணம்</v>
       </c>
       <c r="C47">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="48">
@@ -926,10 +926,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>பொங்கல் விளையாட்டு பணம்</v>
+        <v>அஜீத்குமார்சென்னை</v>
       </c>
       <c r="C48">
-        <v>6000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="49">
@@ -937,10 +937,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>அஜீத்குமார்சென்னை</v>
+        <v>ரவி மணி</v>
       </c>
       <c r="C49">
-        <v>500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="50">
@@ -948,10 +948,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>ரவி மணி</v>
+        <v>வீமன்</v>
       </c>
       <c r="C50">
-        <v>10000</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="51">
@@ -959,10 +959,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>வீமன்</v>
+        <v>குருசாமி (புது தெரு)</v>
       </c>
       <c r="C51">
-        <v>5001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="52">
@@ -970,10 +970,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>குருசாமி (புது தெரு)</v>
+        <v>ராஜு மரகதம்</v>
       </c>
       <c r="C52">
-        <v>2000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="53">
@@ -981,10 +981,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>ராஜு மரகதம்</v>
+        <v>H திருமூர்த்தி</v>
       </c>
       <c r="C53">
-        <v>15000</v>
+        <v>5111</v>
       </c>
     </row>
     <row r="54">
@@ -992,10 +992,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>H திருமூர்த்தி</v>
+        <v>Dr. மோகன்</v>
       </c>
       <c r="C54">
-        <v>5111</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="55">
@@ -1003,10 +1003,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>Dr. மோகன்</v>
+        <v>அதிபன் (மதி டிஃபன்)</v>
       </c>
       <c r="C55">
-        <v>20000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="56">
@@ -1014,10 +1014,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>அதிபன் (மதி டிஃபன்)</v>
+        <v>நாகப்பா ஜவுளி</v>
       </c>
       <c r="C56">
-        <v>1000</v>
+        <v>501</v>
       </c>
     </row>
     <row r="57">
@@ -1025,10 +1025,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>நாகப்பா ஜவுளி</v>
+        <v>சரவணா மெடிக்கல்ஸ்</v>
       </c>
       <c r="C57">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="58">
@@ -1036,10 +1036,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>சரவணா மெடிக்கல்ஸ்</v>
+        <v>சிவகுரு</v>
       </c>
       <c r="C58">
-        <v>500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="59">
@@ -1047,10 +1047,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>சிவகுரு</v>
+        <v>காமராஜ் வாத்தியார்</v>
       </c>
       <c r="C59">
-        <v>5000</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="60">
@@ -1058,10 +1058,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>காமராஜ் வாத்தியார்</v>
+        <v>கிருஷ்ணமூர்த்தி பழனியப்பன்</v>
       </c>
       <c r="C60">
-        <v>5001</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="61">
@@ -1069,10 +1069,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>கிருஷ்ணமூர்த்தி பழனியப்பன்</v>
+        <v>தர்மநாதன் குடும்பத்தார்கள்</v>
       </c>
       <c r="C61">
-        <v>5000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="62">
@@ -1080,10 +1080,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>தர்மநாதன் குடும்பத்தார்கள்</v>
+        <v>ராயல் தாத்தா , கலா முசிறி</v>
       </c>
       <c r="C62">
-        <v>30000</v>
+        <v>15550</v>
       </c>
     </row>
     <row r="63">
@@ -1091,10 +1091,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>ராயல் தாத்தா , கலா முசிறி</v>
+        <v>G. சரண்யா குகநாதன்</v>
       </c>
       <c r="C63">
-        <v>15550</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="64">
@@ -1102,10 +1102,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>G. சரண்யா குகநாதன்</v>
+        <v>மனோஜ்குமார் J</v>
       </c>
       <c r="C64">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="65">
@@ -1113,10 +1113,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>மனோஜ்குமார் J</v>
+        <v>பிரியா கரூர்</v>
       </c>
       <c r="C65">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="66">
@@ -1124,10 +1124,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>பிரியா கரூர்</v>
+        <v>குணா (கணேசன் )</v>
       </c>
       <c r="C66">
-        <v>1001</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="67">
@@ -1135,10 +1135,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>குணா (கணேசன் )</v>
+        <v>பாஸ்கரன் ஓட்டுனர்</v>
       </c>
       <c r="C67">
-        <v>5000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="68">
@@ -1146,10 +1146,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>பாஸ்கரன் ஓட்டுனர்</v>
+        <v>செந்தில் (தங்கராசு)</v>
       </c>
       <c r="C68">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="69">
@@ -1157,10 +1157,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>செந்தில் (தங்கராசு)</v>
+        <v>திவாகர் டிரைவர்  (வேலு)</v>
       </c>
       <c r="C69">
-        <v>5000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="70">
@@ -1168,7 +1168,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>திவாகர் டிரைவர்  (வேலு)</v>
+        <v>கார்த்திக் கரூர் (சாந்தா )</v>
       </c>
       <c r="C70">
         <v>7000</v>
@@ -1179,10 +1179,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>கார்த்திக் கரூர் (சாந்தா )</v>
+        <v>காஞ்சனா அக்கா கரூர்</v>
       </c>
       <c r="C71">
-        <v>7000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="72">
@@ -1190,10 +1190,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>காஞ்சனா அக்கா கரூர்</v>
+        <v>சுரேஷ் (பட்டு)</v>
       </c>
       <c r="C72">
-        <v>2000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73">
@@ -1201,10 +1201,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>சுரேஷ் (பட்டு)</v>
+        <v>சிவகாமி (கண்ணன்)</v>
       </c>
       <c r="C73">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
@@ -1212,10 +1212,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>சிவகாமி (கண்ணன்)</v>
+        <v>சுப்பிரமணி (மயில்)</v>
       </c>
       <c r="C74">
-        <v>50</v>
+        <v>500</v>
       </c>
     </row>
     <row r="75">
@@ -1223,7 +1223,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>சுப்பிரமணி (மயில்)</v>
+        <v>ராமமூர்த்தி போஸ்டல்</v>
       </c>
       <c r="C75">
         <v>500</v>
@@ -1234,10 +1234,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>ராமமூர்த்தி போஸ்டல்</v>
+        <v>மருதை வாத்தியார்</v>
       </c>
       <c r="C76">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="77">
@@ -1245,10 +1245,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>மருதை வாத்தியார்</v>
+        <v>சந்திரமோகன்</v>
       </c>
       <c r="C77">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="78">
@@ -1256,10 +1256,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>சந்திரமோகன்</v>
+        <v>தங்கவேல் (சஞ்சய்)</v>
       </c>
       <c r="C78">
-        <v>3000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="79">
@@ -1267,10 +1267,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>தங்கவேல் (சஞ்சய்)</v>
+        <v>சங்கர் (முதலியார்)</v>
       </c>
       <c r="C79">
-        <v>200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="80">
@@ -1278,10 +1278,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>சங்கர் (முதலியார்)</v>
+        <v>பிச்சைமுத்து</v>
       </c>
       <c r="C80">
-        <v>1001</v>
+        <v>600</v>
       </c>
     </row>
     <row r="81">
@@ -1289,10 +1289,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>பிச்சைமுத்து</v>
+        <v>மேஸ்திரி கணேஷ்</v>
       </c>
       <c r="C81">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82">
@@ -1300,10 +1300,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>மேஸ்திரி கணேஷ்</v>
+        <v>சந்ஜீவுகுமார்</v>
       </c>
       <c r="C82">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="83">
@@ -1311,10 +1311,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>சந்ஜீவுகுமார்</v>
+        <v>புனியமூர்த்தி</v>
       </c>
       <c r="C83">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84">
@@ -1322,7 +1322,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>புனியமூர்த்தி</v>
+        <v>பேபி</v>
       </c>
       <c r="C84">
         <v>100</v>
@@ -1333,10 +1333,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>பேபி</v>
+        <v>லோகநாதன் காத்தமுத்து</v>
       </c>
       <c r="C85">
-        <v>100</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="86">
@@ -1344,10 +1344,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>லோகநாதன் காத்தமுத்து</v>
+        <v>சிவன் பக்தர்கள் SRS</v>
       </c>
       <c r="C86">
-        <v>2026</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="87">
@@ -1355,10 +1355,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>சிவன் பக்தர்கள் SRS</v>
+        <v>விக்னேஷ் ஜெகநாதன்</v>
       </c>
       <c r="C87">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="88">
@@ -1366,10 +1366,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>விக்னேஷ் ஜெகநாதன்</v>
+        <v>அருண் அன்பானந்தன்</v>
       </c>
       <c r="C88">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="89">
@@ -1377,10 +1377,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>அருண் அன்பானந்தன்</v>
+        <v>செல்லதுரை சுலோச்சனா</v>
       </c>
       <c r="C89">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="90">
@@ -1388,10 +1388,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>செல்லதுரை சுலோச்சனா</v>
+        <v>லட்சுமி ராஹவன் தொட்டியம்</v>
       </c>
       <c r="C90">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="91">
@@ -1399,10 +1399,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="str">
-        <v>லட்சுமி ராஹவன் தொட்டியம்</v>
+        <v>சதீஷ் கருக்கமடை</v>
       </c>
       <c r="C91">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="92">
@@ -1410,10 +1410,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="str">
-        <v>சதீஷ் கருக்கமடை</v>
+        <v>சாந்தி ராஜாங்கம் திம்மச்சிபுரம்</v>
       </c>
       <c r="C92">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="93">
@@ -1421,10 +1421,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="str">
-        <v>சாந்தி ராஜாங்கம் திம்மச்சிபுரம்</v>
+        <v>MI செல் ஷோரூம் தொட்டியம்</v>
       </c>
       <c r="C93">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="94">
@@ -1432,10 +1432,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="str">
-        <v>MI செல் ஷோரூம் தொட்டியம்</v>
+        <v>உதயகுமார்</v>
       </c>
       <c r="C94">
-        <v>1000</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="95">
@@ -1443,10 +1443,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="str">
-        <v>உதயகுமார்</v>
+        <v>விவேக்</v>
       </c>
       <c r="C95">
-        <v>1010</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="96">
@@ -1454,10 +1454,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="str">
-        <v>விவேக்</v>
+        <v>பாலமுருகன்(MILK)</v>
       </c>
       <c r="C96">
-        <v>3000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="97">
@@ -1465,10 +1465,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="str">
-        <v>பாலமுருகன்(MILK)</v>
+        <v>பூமதி புது தெரு</v>
       </c>
       <c r="C97">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="98">
@@ -1476,10 +1476,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="str">
-        <v>பூமதி புது தெரு</v>
+        <v>அருண் (WATRE CAN)</v>
       </c>
       <c r="C98">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99">
@@ -1487,10 +1487,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="str">
-        <v>அருண் (WATRE CAN)</v>
+        <v>போஸ்டல் சுப்பிரமணி</v>
       </c>
       <c r="C99">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="100">
@@ -1498,10 +1498,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="str">
-        <v>போஸ்டல் சுப்பிரமணி</v>
+        <v>நல்லுசாமி</v>
       </c>
       <c r="C100">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="101">
@@ -1509,10 +1509,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="str">
-        <v>நல்லுசாமி</v>
+        <v>கல்பனா கரூர்</v>
       </c>
       <c r="C101">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="102">
@@ -1520,10 +1520,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="str">
-        <v>கல்பனா கரூர்</v>
+        <v>கோபால்</v>
       </c>
       <c r="C102">
-        <v>5000</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="103">
@@ -1531,10 +1531,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="str">
-        <v>கோபால்</v>
+        <v>போஸ்டல் பெரியசாமி கரூர்</v>
       </c>
       <c r="C103">
-        <v>10001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="104">
@@ -1542,10 +1542,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="str">
-        <v>போஸ்டல் பெரியசாமி கரூர்</v>
+        <v>பானு(பூபதி)</v>
       </c>
       <c r="C104">
-        <v>5001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="105">
@@ -1553,7 +1553,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="str">
-        <v>பானு(பூபதி)</v>
+        <v>வள்ளி(பூபதி)</v>
       </c>
       <c r="C105">
         <v>2000</v>
@@ -1564,10 +1564,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="str">
-        <v>வள்ளி(பூபதி)</v>
+        <v>லதா(பழனியப்பன்)</v>
       </c>
       <c r="C106">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="107">
@@ -1575,10 +1575,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="str">
-        <v>லதா(பழனியப்பன்)</v>
+        <v>ஜீவா(திருமூர்த்தி)</v>
       </c>
       <c r="C107">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="108">
@@ -1586,10 +1586,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="str">
-        <v>ஜீவா(திருமூர்த்தி)</v>
+        <v>வினோத்(ELECTRITION)</v>
       </c>
       <c r="C108">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="109">
@@ -1597,10 +1597,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="str">
-        <v>வினோத்(ELECTRITION)</v>
+        <v>கருணாநிதி மளிகை</v>
       </c>
       <c r="C109">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="110">
@@ -1608,10 +1608,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="str">
-        <v>கருணாநிதி மளிகை</v>
+        <v>லதா பழனியப்பன்</v>
       </c>
       <c r="C110">
-        <v>1000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="111">
@@ -1619,10 +1619,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="str">
-        <v>லதா பழனியப்பன்</v>
+        <v>மலர்கொடி</v>
       </c>
       <c r="C111">
-        <v>2001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="112">
@@ -1630,10 +1630,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="str">
-        <v>மலர்கொடி</v>
+        <v>சுமன் காவேரி நகர்</v>
       </c>
       <c r="C112">
-        <v>1000</v>
+        <v>501</v>
       </c>
     </row>
     <row r="113">
@@ -1641,10 +1641,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="str">
-        <v>சுமன் காவேரி நகர்</v>
+        <v>நக்கராஜ் இலை வியாபாரம்</v>
       </c>
       <c r="C113">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="114">
@@ -1652,10 +1652,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="str">
-        <v>நக்கராஜ் இலை வியாபாரம்</v>
+        <v>ஆசாரி செல்வம்</v>
       </c>
       <c r="C114">
-        <v>500</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="115">
@@ -1663,10 +1663,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="str">
-        <v>ஆசாரி செல்வம்</v>
+        <v>லோகநாதன் சுப்ரமணியன்</v>
       </c>
       <c r="C115">
-        <v>1005</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="116">
@@ -1674,10 +1674,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="str">
-        <v>லோகநாதன் சுப்ரமணியன்</v>
+        <v>சுதாகர் ஆர்மி</v>
       </c>
       <c r="C116">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="117">
@@ -1685,10 +1685,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="str">
-        <v>சுதாகர் ஆர்மி</v>
+        <v>சின்னசாமி ஊஞ்சி</v>
       </c>
       <c r="C117">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="118">
@@ -1696,10 +1696,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="str">
-        <v>சின்னசாமி ஊஞ்சி</v>
+        <v>ராஜா சார் SRS</v>
       </c>
       <c r="C118">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="119">
@@ -1707,10 +1707,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="str">
-        <v>ராஜா சார் SRS</v>
+        <v>மாரியாயி ஆனடபுரம் குடும்பத்தார்</v>
       </c>
       <c r="C119">
-        <v>2000</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="120">
@@ -1718,10 +1718,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="str">
-        <v>மாரியாயி ஆனடபுரம் குடும்பத்தார்</v>
+        <v>பாலமுருகன் புடலாத்ததி</v>
       </c>
       <c r="C120">
-        <v>11001</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="121">
@@ -1729,10 +1729,10 @@
         <v>120</v>
       </c>
       <c r="B121" t="str">
-        <v>பாலமுருகன் புடலாத்ததி</v>
+        <v>கணேசன் செம்பன்</v>
       </c>
       <c r="C121">
-        <v>10000</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="122">
@@ -1740,10 +1740,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="str">
-        <v>கணேசன் செம்பன்</v>
+        <v>ஜோதிமணி</v>
       </c>
       <c r="C122">
-        <v>5010</v>
+        <v>200</v>
       </c>
     </row>
     <row r="123">
@@ -1751,10 +1751,10 @@
         <v>122</v>
       </c>
       <c r="B123" t="str">
-        <v>ஜோதிமணி</v>
+        <v>குணசேகரன் சித்திரா</v>
       </c>
       <c r="C123">
-        <v>200</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="124">
@@ -1762,10 +1762,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="str">
-        <v>குணசேகரன் சித்திரா</v>
+        <v>தங்கராஜ்</v>
       </c>
       <c r="C124">
-        <v>4001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="125">
@@ -1773,7 +1773,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="str">
-        <v>தங்கராஜ்</v>
+        <v>ரெங்கநாதன்</v>
       </c>
       <c r="C125">
         <v>1000</v>
@@ -1784,7 +1784,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="str">
-        <v>ரெங்கநாதன்</v>
+        <v>ஜெயராஜ்</v>
       </c>
       <c r="C126">
         <v>1000</v>
@@ -1795,7 +1795,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="str">
-        <v>ஜெயராஜ்</v>
+        <v>சரோஜா</v>
       </c>
       <c r="C127">
         <v>1000</v>
@@ -1806,7 +1806,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="str">
-        <v>சரோஜா</v>
+        <v>சுரேஷ் காத்தான்</v>
       </c>
       <c r="C128">
         <v>1000</v>
@@ -1817,10 +1817,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="str">
-        <v>சுரேஷ் காத்தான்</v>
+        <v>மாரியப்பன்</v>
       </c>
       <c r="C129">
-        <v>1000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="130">
@@ -1828,10 +1828,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="str">
-        <v>மாரியப்பன்</v>
+        <v>செல்வம் A1</v>
       </c>
       <c r="C130">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="131">
@@ -1839,10 +1839,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="str">
-        <v>செல்வம் A1</v>
+        <v>தியாகராஜன் சலூன்</v>
       </c>
       <c r="C131">
-        <v>500</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="132">
@@ -1850,10 +1850,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="str">
-        <v>தியாகராஜன் சலூன்</v>
+        <v>சிவகுமார்</v>
       </c>
       <c r="C132">
-        <v>1101</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="133">
@@ -1861,10 +1861,10 @@
         <v>132</v>
       </c>
       <c r="B133" t="str">
-        <v>சிவகுமார்</v>
+        <v>சந்திரன்</v>
       </c>
       <c r="C133">
-        <v>1000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="134">
@@ -1872,10 +1872,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="str">
-        <v>சந்திரன்</v>
+        <v>கும்பாபிசேகம் நாள் நன்கொடை வரவு</v>
       </c>
       <c r="C134">
-        <v>200</v>
+        <v>37688</v>
       </c>
     </row>
     <row r="135">
@@ -1883,10 +1883,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="str">
-        <v>கும்பாபிசேகம் நாள் நன்கொடை வரவு</v>
+        <v>Demo User</v>
       </c>
       <c r="C135">
-        <v>37688</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="136">
@@ -1905,26 +1905,15 @@
         <v>136</v>
       </c>
       <c r="B137" t="str">
-        <v>Demo User</v>
+        <v>testuser</v>
       </c>
       <c r="C137">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138">
-        <v>137</v>
-      </c>
-      <c r="B138" t="str">
-        <v>testuser</v>
-      </c>
-      <c r="C138">
         <v>1332</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C138"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C137"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C137"/>
+  <dimension ref="A1:C136"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -420,7 +420,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Santhosh R</v>
+        <v>Suresh</v>
       </c>
       <c r="C2">
         <v>1000</v>
@@ -431,10 +431,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Suresh</v>
+        <v>ஸ்ரீனிவாச அய்யர்</v>
       </c>
       <c r="C3">
-        <v>1000</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="4">
@@ -442,10 +442,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>ஸ்ரீனிவாச அய்யர்</v>
+        <v>லட்சுமி</v>
       </c>
       <c r="C4">
-        <v>10001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="5">
@@ -453,10 +453,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>லட்சுமி</v>
+        <v>செந்தில் (சக்கரவர்த்தி)</v>
       </c>
       <c r="C5">
-        <v>5001</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="6">
@@ -464,10 +464,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>செந்தில் (சக்கரவர்த்தி)</v>
+        <v>ஆனந்த்</v>
       </c>
       <c r="C6">
-        <v>4700</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="7">
@@ -475,7 +475,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>ஆனந்த்</v>
+        <v>யோகேஷ்</v>
       </c>
       <c r="C7">
         <v>19000</v>
@@ -486,10 +486,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>யோகேஷ்</v>
+        <v>சுரேஷ்</v>
       </c>
       <c r="C8">
-        <v>19000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="9">
@@ -497,10 +497,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>சுரேஷ்</v>
+        <v>பூபதி</v>
       </c>
       <c r="C9">
-        <v>20000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="10">
@@ -508,10 +508,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>பூபதி</v>
+        <v>நந்தகுமார்</v>
       </c>
       <c r="C10">
-        <v>27500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="11">
@@ -519,10 +519,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>நந்தகுமார்</v>
+        <v>ரமேஷ்(டிரைவர்)</v>
       </c>
       <c r="C11">
-        <v>9500</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -530,10 +530,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>ரமேஷ்(டிரைவர்)</v>
+        <v>கண்ணன்(post)</v>
       </c>
       <c r="C12">
-        <v>101</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="13">
@@ -541,10 +541,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>கண்ணன்(post)</v>
+        <v>ரமேஷ்(PC)</v>
       </c>
       <c r="C13">
-        <v>10001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14">
@@ -552,10 +552,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>ரமேஷ்(PC)</v>
+        <v>வெற்றிவேல்</v>
       </c>
       <c r="C14">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="15">
@@ -563,7 +563,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>வெற்றிவேல்</v>
+        <v>ஏ. தினேஷ்குமார்</v>
       </c>
       <c r="C15">
         <v>3000</v>
@@ -574,10 +574,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>ஏ. தினேஷ்குமார்</v>
+        <v>சூர்யா கார்த்தி (சீலைபில்லையர்புதூர்)</v>
       </c>
       <c r="C16">
-        <v>3000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="17">
@@ -585,10 +585,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>சூர்யா கார்த்தி (சீலைபில்லையர்புதூர்)</v>
+        <v>சுஜிதா ஈரோடு</v>
       </c>
       <c r="C17">
-        <v>12000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="18">
@@ -596,10 +596,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>சுஜிதா ஈரோடு</v>
+        <v>நாகராஜ் அய்யர்</v>
       </c>
       <c r="C18">
-        <v>2000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19">
@@ -607,10 +607,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>நாகராஜ் அய்யர்</v>
+        <v>நட்ராஜ் கோவை (மணி)</v>
       </c>
       <c r="C19">
-        <v>500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="20">
@@ -618,10 +618,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>நட்ராஜ் கோவை (மணி)</v>
+        <v>தனலட்சுமி புகழேந்தி</v>
       </c>
       <c r="C20">
-        <v>5500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21">
@@ -629,10 +629,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>தனலட்சுமி புகழேந்தி</v>
+        <v>ராஜசேகர் பழனியப்பன்</v>
       </c>
       <c r="C21">
-        <v>500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="22">
@@ -640,10 +640,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>ராஜசேகர் பழனியப்பன்</v>
+        <v>நடராஜன் சைக்கிள்</v>
       </c>
       <c r="C22">
-        <v>10000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>நடராஜன் சைக்கிள்</v>
+        <v>எவுரி (postal)</v>
       </c>
       <c r="C23">
-        <v>1000</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="24">
@@ -662,10 +662,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>எவுரி (postal)</v>
+        <v>அருண் இரத்த பரிசோதனை (காட்டுபுத்தூர்)</v>
       </c>
       <c r="C24">
-        <v>5001</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="25">
@@ -673,10 +673,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>அருண் இரத்த பரிசோதனை (காட்டுபுத்தூர்)</v>
+        <v>ராஜேந்திரன் சுப்ரமணி</v>
       </c>
       <c r="C25">
-        <v>15000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="26">
@@ -684,10 +684,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>ராஜேந்திரன் சுப்ரமணி</v>
+        <v>சந்தோஸ் ரமேஷ்</v>
       </c>
       <c r="C26">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="27">
@@ -695,10 +695,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>சந்தோஸ் ரமேஷ்</v>
+        <v>ரமேஷ் பன்னீர்செல்வம்</v>
       </c>
       <c r="C27">
-        <v>10000</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="28">
@@ -706,10 +706,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>ரமேஷ் பன்னீர்செல்வம்</v>
+        <v>முத்துகிருஷ்ணன்</v>
       </c>
       <c r="C28">
-        <v>10001</v>
+        <v>5501</v>
       </c>
     </row>
     <row r="29">
@@ -717,10 +717,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>முத்துகிருஷ்ணன்</v>
+        <v>சுபாஷினி காட்டுப்புத்தூர்</v>
       </c>
       <c r="C29">
-        <v>5501</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="30">
@@ -728,10 +728,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>சுபாஷினி காட்டுப்புத்தூர்</v>
+        <v>அமுதா அன்பாநந்தன்</v>
       </c>
       <c r="C30">
-        <v>1000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="31">
@@ -739,10 +739,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>அமுதா அன்பாநந்தன்</v>
+        <v>கமல்நாத் கொளக்குடி</v>
       </c>
       <c r="C31">
-        <v>12500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32">
@@ -750,10 +750,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>கமல்நாத் கொளக்குடி</v>
+        <v>ஸ்ரீனிவாசபிரபு</v>
       </c>
       <c r="C32">
-        <v>300</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="33">
@@ -761,10 +761,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>ஸ்ரீனிவாசபிரபு</v>
+        <v>நாகவேல்</v>
       </c>
       <c r="C33">
-        <v>5001</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="34">
@@ -772,10 +772,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>நாகவேல்</v>
+        <v>செல்வராஜ் (TNEB)</v>
       </c>
       <c r="C34">
-        <v>17500</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="35">
@@ -783,7 +783,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>செல்வராஜ் (TNEB)</v>
+        <v>சதிஸ்குமார் (VAO)</v>
       </c>
       <c r="C35">
         <v>10001</v>
@@ -794,10 +794,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>சதிஸ்குமார் (VAO)</v>
+        <v>சரவணன் சதாசிவம்</v>
       </c>
       <c r="C36">
-        <v>10001</v>
+        <v>10501</v>
       </c>
     </row>
     <row r="37">
@@ -805,10 +805,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>சரவணன் சதாசிவம்</v>
+        <v>பிரியா நரேந்தரகுமார்</v>
       </c>
       <c r="C37">
-        <v>10501</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="38">
@@ -816,10 +816,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>பிரியா நரேந்தரகுமார்</v>
+        <v>புகழேந்தி டைலர்</v>
       </c>
       <c r="C38">
-        <v>1001</v>
+        <v>700</v>
       </c>
     </row>
     <row r="39">
@@ -827,10 +827,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>புகழேந்தி டைலர்</v>
+        <v>தங்கராசு கிருஷ்ணன்</v>
       </c>
       <c r="C39">
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="40">
@@ -838,10 +838,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>தங்கராசு கிருஷ்ணன்</v>
+        <v>சரவணன் ராஜசுந்தரி (தொட்டியம்)</v>
       </c>
       <c r="C40">
-        <v>2000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="41">
@@ -849,10 +849,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>சரவணன் ராஜசுந்தரி (தொட்டியம்)</v>
+        <v>ரெங்கநாதன் ரைஸ் மில்</v>
       </c>
       <c r="C41">
-        <v>10000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="42">
@@ -860,10 +860,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>ரெங்கநாதன் ரைஸ் மில்</v>
+        <v>வினோத் நீலமேகம்</v>
       </c>
       <c r="C42">
-        <v>25000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="43">
@@ -871,10 +871,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>வினோத் நீலமேகம்</v>
+        <v>சூர்யகுமார்</v>
       </c>
       <c r="C43">
-        <v>1000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="44">
@@ -882,10 +882,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>சூர்யகுமார்</v>
+        <v>சிவஞானம் ரெத்தினவேல்</v>
       </c>
       <c r="C44">
-        <v>2500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="45">
@@ -893,7 +893,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>சிவஞானம் ரெத்தினவேல்</v>
+        <v>நடராஜன் வாத்தியார்</v>
       </c>
       <c r="C45">
         <v>5000</v>
@@ -904,10 +904,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>நடராஜன் வாத்தியார்</v>
+        <v>பொங்கல் விளையாட்டு பணம்</v>
       </c>
       <c r="C46">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="47">
@@ -915,10 +915,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>பொங்கல் விளையாட்டு பணம்</v>
+        <v>அஜீத்குமார்சென்னை</v>
       </c>
       <c r="C47">
-        <v>6000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="48">
@@ -926,10 +926,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>அஜீத்குமார்சென்னை</v>
+        <v>ரவி மணி</v>
       </c>
       <c r="C48">
-        <v>500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="49">
@@ -937,10 +937,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>ரவி மணி</v>
+        <v>வீமன்</v>
       </c>
       <c r="C49">
-        <v>10000</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="50">
@@ -948,10 +948,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>வீமன்</v>
+        <v>குருசாமி (புது தெரு)</v>
       </c>
       <c r="C50">
-        <v>5001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="51">
@@ -959,10 +959,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>குருசாமி (புது தெரு)</v>
+        <v>ராஜு மரகதம்</v>
       </c>
       <c r="C51">
-        <v>2000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="52">
@@ -970,10 +970,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>ராஜு மரகதம்</v>
+        <v>H திருமூர்த்தி</v>
       </c>
       <c r="C52">
-        <v>15000</v>
+        <v>5111</v>
       </c>
     </row>
     <row r="53">
@@ -981,10 +981,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>H திருமூர்த்தி</v>
+        <v>Dr. மோகன்</v>
       </c>
       <c r="C53">
-        <v>5111</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="54">
@@ -992,10 +992,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>Dr. மோகன்</v>
+        <v>அதிபன் (மதி டிஃபன்)</v>
       </c>
       <c r="C54">
-        <v>20000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="55">
@@ -1003,10 +1003,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>அதிபன் (மதி டிஃபன்)</v>
+        <v>நாகப்பா ஜவுளி</v>
       </c>
       <c r="C55">
-        <v>1000</v>
+        <v>501</v>
       </c>
     </row>
     <row r="56">
@@ -1014,10 +1014,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>நாகப்பா ஜவுளி</v>
+        <v>சரவணா மெடிக்கல்ஸ்</v>
       </c>
       <c r="C56">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="57">
@@ -1025,10 +1025,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>சரவணா மெடிக்கல்ஸ்</v>
+        <v>சிவகுரு</v>
       </c>
       <c r="C57">
-        <v>500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="58">
@@ -1036,10 +1036,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>சிவகுரு</v>
+        <v>காமராஜ் வாத்தியார்</v>
       </c>
       <c r="C58">
-        <v>5000</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="59">
@@ -1047,10 +1047,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>காமராஜ் வாத்தியார்</v>
+        <v>கிருஷ்ணமூர்த்தி பழனியப்பன்</v>
       </c>
       <c r="C59">
-        <v>5001</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="60">
@@ -1058,10 +1058,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>கிருஷ்ணமூர்த்தி பழனியப்பன்</v>
+        <v>தர்மநாதன் குடும்பத்தார்கள்</v>
       </c>
       <c r="C60">
-        <v>5000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="61">
@@ -1069,10 +1069,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>தர்மநாதன் குடும்பத்தார்கள்</v>
+        <v>ராயல் தாத்தா , கலா முசிறி</v>
       </c>
       <c r="C61">
-        <v>30000</v>
+        <v>15550</v>
       </c>
     </row>
     <row r="62">
@@ -1080,10 +1080,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>ராயல் தாத்தா , கலா முசிறி</v>
+        <v>G. சரண்யா குகநாதன்</v>
       </c>
       <c r="C62">
-        <v>15550</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="63">
@@ -1091,10 +1091,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>G. சரண்யா குகநாதன்</v>
+        <v>மனோஜ்குமார் J</v>
       </c>
       <c r="C63">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="64">
@@ -1102,10 +1102,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>மனோஜ்குமார் J</v>
+        <v>பிரியா கரூர்</v>
       </c>
       <c r="C64">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="65">
@@ -1113,10 +1113,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>பிரியா கரூர்</v>
+        <v>குணா (கணேசன் )</v>
       </c>
       <c r="C65">
-        <v>1001</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="66">
@@ -1124,10 +1124,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>குணா (கணேசன் )</v>
+        <v>பாஸ்கரன் ஓட்டுனர்</v>
       </c>
       <c r="C66">
-        <v>5000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="67">
@@ -1135,10 +1135,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>பாஸ்கரன் ஓட்டுனர்</v>
+        <v>செந்தில் (தங்கராசு)</v>
       </c>
       <c r="C67">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="68">
@@ -1146,10 +1146,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>செந்தில் (தங்கராசு)</v>
+        <v>திவாகர் டிரைவர்  (வேலு)</v>
       </c>
       <c r="C68">
-        <v>5000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="69">
@@ -1157,7 +1157,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>திவாகர் டிரைவர்  (வேலு)</v>
+        <v>கார்த்திக் கரூர் (சாந்தா )</v>
       </c>
       <c r="C69">
         <v>7000</v>
@@ -1168,10 +1168,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>கார்த்திக் கரூர் (சாந்தா )</v>
+        <v>காஞ்சனா அக்கா கரூர்</v>
       </c>
       <c r="C70">
-        <v>7000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="71">
@@ -1179,10 +1179,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>காஞ்சனா அக்கா கரூர்</v>
+        <v>சுரேஷ் (பட்டு)</v>
       </c>
       <c r="C71">
-        <v>2000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72">
@@ -1190,10 +1190,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>சுரேஷ் (பட்டு)</v>
+        <v>சிவகாமி (கண்ணன்)</v>
       </c>
       <c r="C72">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73">
@@ -1201,10 +1201,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>சிவகாமி (கண்ணன்)</v>
+        <v>சுப்பிரமணி (மயில்)</v>
       </c>
       <c r="C73">
-        <v>50</v>
+        <v>500</v>
       </c>
     </row>
     <row r="74">
@@ -1212,7 +1212,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>சுப்பிரமணி (மயில்)</v>
+        <v>ராமமூர்த்தி போஸ்டல்</v>
       </c>
       <c r="C74">
         <v>500</v>
@@ -1223,10 +1223,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>ராமமூர்த்தி போஸ்டல்</v>
+        <v>மருதை வாத்தியார்</v>
       </c>
       <c r="C75">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="76">
@@ -1234,10 +1234,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>மருதை வாத்தியார்</v>
+        <v>சந்திரமோகன்</v>
       </c>
       <c r="C76">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="77">
@@ -1245,10 +1245,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>சந்திரமோகன்</v>
+        <v>தங்கவேல் (சஞ்சய்)</v>
       </c>
       <c r="C77">
-        <v>3000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="78">
@@ -1256,10 +1256,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>தங்கவேல் (சஞ்சய்)</v>
+        <v>சங்கர் (முதலியார்)</v>
       </c>
       <c r="C78">
-        <v>200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="79">
@@ -1267,10 +1267,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>சங்கர் (முதலியார்)</v>
+        <v>பிச்சைமுத்து</v>
       </c>
       <c r="C79">
-        <v>1001</v>
+        <v>600</v>
       </c>
     </row>
     <row r="80">
@@ -1278,10 +1278,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>பிச்சைமுத்து</v>
+        <v>மேஸ்திரி கணேஷ்</v>
       </c>
       <c r="C80">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81">
@@ -1289,10 +1289,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>மேஸ்திரி கணேஷ்</v>
+        <v>சந்ஜீவுகுமார்</v>
       </c>
       <c r="C81">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="82">
@@ -1300,10 +1300,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>சந்ஜீவுகுமார்</v>
+        <v>புனியமூர்த்தி</v>
       </c>
       <c r="C82">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="83">
@@ -1311,7 +1311,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>புனியமூர்த்தி</v>
+        <v>பேபி</v>
       </c>
       <c r="C83">
         <v>100</v>
@@ -1322,10 +1322,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>பேபி</v>
+        <v>லோகநாதன் காத்தமுத்து</v>
       </c>
       <c r="C84">
-        <v>100</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="85">
@@ -1333,10 +1333,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>லோகநாதன் காத்தமுத்து</v>
+        <v>சிவன் பக்தர்கள் SRS</v>
       </c>
       <c r="C85">
-        <v>2026</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="86">
@@ -1344,10 +1344,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>சிவன் பக்தர்கள் SRS</v>
+        <v>விக்னேஷ் ஜெகநாதன்</v>
       </c>
       <c r="C86">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="87">
@@ -1355,10 +1355,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>விக்னேஷ் ஜெகநாதன்</v>
+        <v>அருண் அன்பானந்தன்</v>
       </c>
       <c r="C87">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="88">
@@ -1366,10 +1366,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>அருண் அன்பானந்தன்</v>
+        <v>செல்லதுரை சுலோச்சனா</v>
       </c>
       <c r="C88">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="89">
@@ -1377,10 +1377,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>செல்லதுரை சுலோச்சனா</v>
+        <v>லட்சுமி ராஹவன் தொட்டியம்</v>
       </c>
       <c r="C89">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="90">
@@ -1388,10 +1388,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>லட்சுமி ராஹவன் தொட்டியம்</v>
+        <v>சதீஷ் கருக்கமடை</v>
       </c>
       <c r="C90">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="91">
@@ -1399,10 +1399,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="str">
-        <v>சதீஷ் கருக்கமடை</v>
+        <v>சாந்தி ராஜாங்கம் திம்மச்சிபுரம்</v>
       </c>
       <c r="C91">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="92">
@@ -1410,10 +1410,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="str">
-        <v>சாந்தி ராஜாங்கம் திம்மச்சிபுரம்</v>
+        <v>MI செல் ஷோரூம் தொட்டியம்</v>
       </c>
       <c r="C92">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="93">
@@ -1421,10 +1421,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="str">
-        <v>MI செல் ஷோரூம் தொட்டியம்</v>
+        <v>உதயகுமார்</v>
       </c>
       <c r="C93">
-        <v>1000</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="94">
@@ -1432,10 +1432,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="str">
-        <v>உதயகுமார்</v>
+        <v>விவேக்</v>
       </c>
       <c r="C94">
-        <v>1010</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="95">
@@ -1443,10 +1443,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="str">
-        <v>விவேக்</v>
+        <v>பாலமுருகன்(MILK)</v>
       </c>
       <c r="C95">
-        <v>3000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="96">
@@ -1454,10 +1454,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="str">
-        <v>பாலமுருகன்(MILK)</v>
+        <v>பூமதி புது தெரு</v>
       </c>
       <c r="C96">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="97">
@@ -1465,10 +1465,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="str">
-        <v>பூமதி புது தெரு</v>
+        <v>அருண் (WATRE CAN)</v>
       </c>
       <c r="C97">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="98">
@@ -1476,10 +1476,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="str">
-        <v>அருண் (WATRE CAN)</v>
+        <v>போஸ்டல் சுப்பிரமணி</v>
       </c>
       <c r="C98">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="99">
@@ -1487,10 +1487,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="str">
-        <v>போஸ்டல் சுப்பிரமணி</v>
+        <v>நல்லுசாமி</v>
       </c>
       <c r="C99">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="100">
@@ -1498,10 +1498,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="str">
-        <v>நல்லுசாமி</v>
+        <v>கல்பனா கரூர்</v>
       </c>
       <c r="C100">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="101">
@@ -1509,10 +1509,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="str">
-        <v>கல்பனா கரூர்</v>
+        <v>கோபால்</v>
       </c>
       <c r="C101">
-        <v>5000</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="102">
@@ -1520,10 +1520,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="str">
-        <v>கோபால்</v>
+        <v>போஸ்டல் பெரியசாமி கரூர்</v>
       </c>
       <c r="C102">
-        <v>10001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="103">
@@ -1531,10 +1531,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="str">
-        <v>போஸ்டல் பெரியசாமி கரூர்</v>
+        <v>பானு(பூபதி)</v>
       </c>
       <c r="C103">
-        <v>5001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="104">
@@ -1542,7 +1542,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="str">
-        <v>பானு(பூபதி)</v>
+        <v>வள்ளி(பூபதி)</v>
       </c>
       <c r="C104">
         <v>2000</v>
@@ -1553,10 +1553,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="str">
-        <v>வள்ளி(பூபதி)</v>
+        <v>லதா(பழனியப்பன்)</v>
       </c>
       <c r="C105">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="106">
@@ -1564,10 +1564,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="str">
-        <v>லதா(பழனியப்பன்)</v>
+        <v>ஜீவா(திருமூர்த்தி)</v>
       </c>
       <c r="C106">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="107">
@@ -1575,10 +1575,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="str">
-        <v>ஜீவா(திருமூர்த்தி)</v>
+        <v>வினோத்(ELECTRITION)</v>
       </c>
       <c r="C107">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="108">
@@ -1586,10 +1586,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="str">
-        <v>வினோத்(ELECTRITION)</v>
+        <v>கருணாநிதி மளிகை</v>
       </c>
       <c r="C108">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="109">
@@ -1597,10 +1597,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="str">
-        <v>கருணாநிதி மளிகை</v>
+        <v>லதா பழனியப்பன்</v>
       </c>
       <c r="C109">
-        <v>1000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="110">
@@ -1608,10 +1608,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="str">
-        <v>லதா பழனியப்பன்</v>
+        <v>மலர்கொடி</v>
       </c>
       <c r="C110">
-        <v>2001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="111">
@@ -1619,10 +1619,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="str">
-        <v>மலர்கொடி</v>
+        <v>சுமன் காவேரி நகர்</v>
       </c>
       <c r="C111">
-        <v>1000</v>
+        <v>501</v>
       </c>
     </row>
     <row r="112">
@@ -1630,10 +1630,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="str">
-        <v>சுமன் காவேரி நகர்</v>
+        <v>நக்கராஜ் இலை வியாபாரம்</v>
       </c>
       <c r="C112">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="113">
@@ -1641,10 +1641,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="str">
-        <v>நக்கராஜ் இலை வியாபாரம்</v>
+        <v>ஆசாரி செல்வம்</v>
       </c>
       <c r="C113">
-        <v>500</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="114">
@@ -1652,10 +1652,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="str">
-        <v>ஆசாரி செல்வம்</v>
+        <v>லோகநாதன் சுப்ரமணியன்</v>
       </c>
       <c r="C114">
-        <v>1005</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="115">
@@ -1663,10 +1663,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="str">
-        <v>லோகநாதன் சுப்ரமணியன்</v>
+        <v>சுதாகர் ஆர்மி</v>
       </c>
       <c r="C115">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="116">
@@ -1674,10 +1674,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="str">
-        <v>சுதாகர் ஆர்மி</v>
+        <v>சின்னசாமி ஊஞ்சி</v>
       </c>
       <c r="C116">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="117">
@@ -1685,10 +1685,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="str">
-        <v>சின்னசாமி ஊஞ்சி</v>
+        <v>ராஜா சார் SRS</v>
       </c>
       <c r="C117">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="118">
@@ -1696,10 +1696,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="str">
-        <v>ராஜா சார் SRS</v>
+        <v>மாரியாயி ஆனடபுரம் குடும்பத்தார்</v>
       </c>
       <c r="C118">
-        <v>2000</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="119">
@@ -1707,10 +1707,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="str">
-        <v>மாரியாயி ஆனடபுரம் குடும்பத்தார்</v>
+        <v>பாலமுருகன் புடலாத்ததி</v>
       </c>
       <c r="C119">
-        <v>11001</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="120">
@@ -1718,10 +1718,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="str">
-        <v>பாலமுருகன் புடலாத்ததி</v>
+        <v>கணேசன் செம்பன்</v>
       </c>
       <c r="C120">
-        <v>10000</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="121">
@@ -1729,10 +1729,10 @@
         <v>120</v>
       </c>
       <c r="B121" t="str">
-        <v>கணேசன் செம்பன்</v>
+        <v>ஜோதிமணி</v>
       </c>
       <c r="C121">
-        <v>5010</v>
+        <v>200</v>
       </c>
     </row>
     <row r="122">
@@ -1740,10 +1740,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="str">
-        <v>ஜோதிமணி</v>
+        <v>குணசேகரன் சித்திரா</v>
       </c>
       <c r="C122">
-        <v>200</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="123">
@@ -1751,10 +1751,10 @@
         <v>122</v>
       </c>
       <c r="B123" t="str">
-        <v>குணசேகரன் சித்திரா</v>
+        <v>தங்கராஜ்</v>
       </c>
       <c r="C123">
-        <v>4001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="124">
@@ -1762,7 +1762,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="str">
-        <v>தங்கராஜ்</v>
+        <v>ரெங்கநாதன்</v>
       </c>
       <c r="C124">
         <v>1000</v>
@@ -1773,7 +1773,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="str">
-        <v>ரெங்கநாதன்</v>
+        <v>ஜெயராஜ்</v>
       </c>
       <c r="C125">
         <v>1000</v>
@@ -1784,7 +1784,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="str">
-        <v>ஜெயராஜ்</v>
+        <v>சரோஜா</v>
       </c>
       <c r="C126">
         <v>1000</v>
@@ -1795,7 +1795,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="str">
-        <v>சரோஜா</v>
+        <v>சுரேஷ் காத்தான்</v>
       </c>
       <c r="C127">
         <v>1000</v>
@@ -1806,10 +1806,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="str">
-        <v>சுரேஷ் காத்தான்</v>
+        <v>மாரியப்பன்</v>
       </c>
       <c r="C128">
-        <v>1000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="129">
@@ -1817,10 +1817,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="str">
-        <v>மாரியப்பன்</v>
+        <v>செல்வம் A1</v>
       </c>
       <c r="C129">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="130">
@@ -1828,10 +1828,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="str">
-        <v>செல்வம் A1</v>
+        <v>தியாகராஜன் சலூன்</v>
       </c>
       <c r="C130">
-        <v>500</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="131">
@@ -1839,10 +1839,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="str">
-        <v>தியாகராஜன் சலூன்</v>
+        <v>சிவகுமார்</v>
       </c>
       <c r="C131">
-        <v>1101</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="132">
@@ -1850,10 +1850,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="str">
-        <v>சிவகுமார்</v>
+        <v>சந்திரன்</v>
       </c>
       <c r="C132">
-        <v>1000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="133">
@@ -1861,10 +1861,10 @@
         <v>132</v>
       </c>
       <c r="B133" t="str">
-        <v>சந்திரன்</v>
+        <v>கும்பாபிசேகம் நாள் நன்கொடை வரவு</v>
       </c>
       <c r="C133">
-        <v>200</v>
+        <v>37688</v>
       </c>
     </row>
     <row r="134">
@@ -1872,10 +1872,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="str">
-        <v>கும்பாபிசேகம் நாள் நன்கொடை வரவு</v>
+        <v>Demo User</v>
       </c>
       <c r="C134">
-        <v>37688</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="135">
@@ -1894,26 +1894,15 @@
         <v>135</v>
       </c>
       <c r="B136" t="str">
-        <v>Demo User</v>
+        <v>testuser</v>
       </c>
       <c r="C136">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137">
-        <v>136</v>
-      </c>
-      <c r="B137" t="str">
-        <v>testuser</v>
-      </c>
-      <c r="C137">
         <v>1332</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C137"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C136"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C136"/>
+  <dimension ref="A1:C135"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -420,10 +420,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Suresh</v>
+        <v>ஸ்ரீனிவாச அய்யர்</v>
       </c>
       <c r="C2">
-        <v>1000</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="3">
@@ -431,10 +431,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>ஸ்ரீனிவாச அய்யர்</v>
+        <v>லட்சுமி</v>
       </c>
       <c r="C3">
-        <v>10001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="4">
@@ -442,10 +442,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>லட்சுமி</v>
+        <v>செந்தில் (சக்கரவர்த்தி)</v>
       </c>
       <c r="C4">
-        <v>5001</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="5">
@@ -453,10 +453,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>செந்தில் (சக்கரவர்த்தி)</v>
+        <v>ஆனந்த்</v>
       </c>
       <c r="C5">
-        <v>4700</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="6">
@@ -464,7 +464,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>ஆனந்த்</v>
+        <v>யோகேஷ்</v>
       </c>
       <c r="C6">
         <v>19000</v>
@@ -475,10 +475,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>யோகேஷ்</v>
+        <v>சுரேஷ்</v>
       </c>
       <c r="C7">
-        <v>19000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>சுரேஷ்</v>
+        <v>பூபதி</v>
       </c>
       <c r="C8">
-        <v>20000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="9">
@@ -497,10 +497,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>பூபதி</v>
+        <v>நந்தகுமார்</v>
       </c>
       <c r="C9">
-        <v>27500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="10">
@@ -508,10 +508,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>நந்தகுமார்</v>
+        <v>ரமேஷ்(டிரைவர்)</v>
       </c>
       <c r="C10">
-        <v>9500</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
@@ -519,10 +519,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>ரமேஷ்(டிரைவர்)</v>
+        <v>கண்ணன்(post)</v>
       </c>
       <c r="C11">
-        <v>101</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="12">
@@ -530,10 +530,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>கண்ணன்(post)</v>
+        <v>ரமேஷ்(PC)</v>
       </c>
       <c r="C12">
-        <v>10001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
@@ -541,10 +541,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>ரமேஷ்(PC)</v>
+        <v>வெற்றிவேல்</v>
       </c>
       <c r="C13">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="14">
@@ -552,7 +552,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>வெற்றிவேல்</v>
+        <v>ஏ. தினேஷ்குமார்</v>
       </c>
       <c r="C14">
         <v>3000</v>
@@ -563,10 +563,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>ஏ. தினேஷ்குமார்</v>
+        <v>சூர்யா கார்த்தி (சீலைபில்லையர்புதூர்)</v>
       </c>
       <c r="C15">
-        <v>3000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="16">
@@ -574,10 +574,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>சூர்யா கார்த்தி (சீலைபில்லையர்புதூர்)</v>
+        <v>சுஜிதா ஈரோடு</v>
       </c>
       <c r="C16">
-        <v>12000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="17">
@@ -585,10 +585,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>சுஜிதா ஈரோடு</v>
+        <v>நாகராஜ் அய்யர்</v>
       </c>
       <c r="C17">
-        <v>2000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18">
@@ -596,10 +596,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>நாகராஜ் அய்யர்</v>
+        <v>நட்ராஜ் கோவை (மணி)</v>
       </c>
       <c r="C18">
-        <v>500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="19">
@@ -607,10 +607,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>நட்ராஜ் கோவை (மணி)</v>
+        <v>தனலட்சுமி புகழேந்தி</v>
       </c>
       <c r="C19">
-        <v>5500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20">
@@ -618,10 +618,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>தனலட்சுமி புகழேந்தி</v>
+        <v>ராஜசேகர் பழனியப்பன்</v>
       </c>
       <c r="C20">
-        <v>500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="21">
@@ -629,10 +629,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>ராஜசேகர் பழனியப்பன்</v>
+        <v>நடராஜன் சைக்கிள்</v>
       </c>
       <c r="C21">
-        <v>10000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="22">
@@ -640,10 +640,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>நடராஜன் சைக்கிள்</v>
+        <v>எவுரி (postal)</v>
       </c>
       <c r="C22">
-        <v>1000</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>எவுரி (postal)</v>
+        <v>அருண் இரத்த பரிசோதனை (காட்டுபுத்தூர்)</v>
       </c>
       <c r="C23">
-        <v>5001</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="24">
@@ -662,10 +662,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>அருண் இரத்த பரிசோதனை (காட்டுபுத்தூர்)</v>
+        <v>ராஜேந்திரன் சுப்ரமணி</v>
       </c>
       <c r="C24">
-        <v>15000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="25">
@@ -673,10 +673,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>ராஜேந்திரன் சுப்ரமணி</v>
+        <v>சந்தோஸ் ரமேஷ்</v>
       </c>
       <c r="C25">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="26">
@@ -684,10 +684,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>சந்தோஸ் ரமேஷ்</v>
+        <v>ரமேஷ் பன்னீர்செல்வம்</v>
       </c>
       <c r="C26">
-        <v>10000</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="27">
@@ -695,10 +695,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>ரமேஷ் பன்னீர்செல்வம்</v>
+        <v>முத்துகிருஷ்ணன்</v>
       </c>
       <c r="C27">
-        <v>10001</v>
+        <v>5501</v>
       </c>
     </row>
     <row r="28">
@@ -706,10 +706,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>முத்துகிருஷ்ணன்</v>
+        <v>சுபாஷினி காட்டுப்புத்தூர்</v>
       </c>
       <c r="C28">
-        <v>5501</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29">
@@ -717,10 +717,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>சுபாஷினி காட்டுப்புத்தூர்</v>
+        <v>அமுதா அன்பாநந்தன்</v>
       </c>
       <c r="C29">
-        <v>1000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="30">
@@ -728,10 +728,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>அமுதா அன்பாநந்தன்</v>
+        <v>கமல்நாத் கொளக்குடி</v>
       </c>
       <c r="C30">
-        <v>12500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
@@ -739,10 +739,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>கமல்நாத் கொளக்குடி</v>
+        <v>ஸ்ரீனிவாசபிரபு</v>
       </c>
       <c r="C31">
-        <v>300</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="32">
@@ -750,10 +750,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>ஸ்ரீனிவாசபிரபு</v>
+        <v>நாகவேல்</v>
       </c>
       <c r="C32">
-        <v>5001</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="33">
@@ -761,10 +761,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>நாகவேல்</v>
+        <v>செல்வராஜ் (TNEB)</v>
       </c>
       <c r="C33">
-        <v>17500</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="34">
@@ -772,7 +772,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>செல்வராஜ் (TNEB)</v>
+        <v>சதிஸ்குமார் (VAO)</v>
       </c>
       <c r="C34">
         <v>10001</v>
@@ -783,10 +783,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>சதிஸ்குமார் (VAO)</v>
+        <v>சரவணன் சதாசிவம்</v>
       </c>
       <c r="C35">
-        <v>10001</v>
+        <v>10501</v>
       </c>
     </row>
     <row r="36">
@@ -794,10 +794,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>சரவணன் சதாசிவம்</v>
+        <v>பிரியா நரேந்தரகுமார்</v>
       </c>
       <c r="C36">
-        <v>10501</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="37">
@@ -805,10 +805,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>பிரியா நரேந்தரகுமார்</v>
+        <v>புகழேந்தி டைலர்</v>
       </c>
       <c r="C37">
-        <v>1001</v>
+        <v>700</v>
       </c>
     </row>
     <row r="38">
@@ -816,10 +816,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>புகழேந்தி டைலர்</v>
+        <v>தங்கராசு கிருஷ்ணன்</v>
       </c>
       <c r="C38">
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="39">
@@ -827,10 +827,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>தங்கராசு கிருஷ்ணன்</v>
+        <v>சரவணன் ராஜசுந்தரி (தொட்டியம்)</v>
       </c>
       <c r="C39">
-        <v>2000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="40">
@@ -838,10 +838,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>சரவணன் ராஜசுந்தரி (தொட்டியம்)</v>
+        <v>ரெங்கநாதன் ரைஸ் மில்</v>
       </c>
       <c r="C40">
-        <v>10000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="41">
@@ -849,10 +849,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>ரெங்கநாதன் ரைஸ் மில்</v>
+        <v>வினோத் நீலமேகம்</v>
       </c>
       <c r="C41">
-        <v>25000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="42">
@@ -860,10 +860,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>வினோத் நீலமேகம்</v>
+        <v>சூர்யகுமார்</v>
       </c>
       <c r="C42">
-        <v>1000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="43">
@@ -871,10 +871,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>சூர்யகுமார்</v>
+        <v>சிவஞானம் ரெத்தினவேல்</v>
       </c>
       <c r="C43">
-        <v>2500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="44">
@@ -882,7 +882,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>சிவஞானம் ரெத்தினவேல்</v>
+        <v>நடராஜன் வாத்தியார்</v>
       </c>
       <c r="C44">
         <v>5000</v>
@@ -893,10 +893,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>நடராஜன் வாத்தியார்</v>
+        <v>பொங்கல் விளையாட்டு பணம்</v>
       </c>
       <c r="C45">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="46">
@@ -904,10 +904,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>பொங்கல் விளையாட்டு பணம்</v>
+        <v>அஜீத்குமார்சென்னை</v>
       </c>
       <c r="C46">
-        <v>6000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="47">
@@ -915,10 +915,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>அஜீத்குமார்சென்னை</v>
+        <v>ரவி மணி</v>
       </c>
       <c r="C47">
-        <v>500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="48">
@@ -926,10 +926,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>ரவி மணி</v>
+        <v>வீமன்</v>
       </c>
       <c r="C48">
-        <v>10000</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="49">
@@ -937,10 +937,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>வீமன்</v>
+        <v>குருசாமி (புது தெரு)</v>
       </c>
       <c r="C49">
-        <v>5001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="50">
@@ -948,10 +948,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>குருசாமி (புது தெரு)</v>
+        <v>ராஜு மரகதம்</v>
       </c>
       <c r="C50">
-        <v>2000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="51">
@@ -959,10 +959,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>ராஜு மரகதம்</v>
+        <v>H திருமூர்த்தி</v>
       </c>
       <c r="C51">
-        <v>15000</v>
+        <v>5111</v>
       </c>
     </row>
     <row r="52">
@@ -970,10 +970,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>H திருமூர்த்தி</v>
+        <v>Dr. மோகன்</v>
       </c>
       <c r="C52">
-        <v>5111</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="53">
@@ -981,10 +981,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>Dr. மோகன்</v>
+        <v>அதிபன் (மதி டிஃபன்)</v>
       </c>
       <c r="C53">
-        <v>20000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="54">
@@ -992,10 +992,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>அதிபன் (மதி டிஃபன்)</v>
+        <v>நாகப்பா ஜவுளி</v>
       </c>
       <c r="C54">
-        <v>1000</v>
+        <v>501</v>
       </c>
     </row>
     <row r="55">
@@ -1003,10 +1003,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>நாகப்பா ஜவுளி</v>
+        <v>சரவணா மெடிக்கல்ஸ்</v>
       </c>
       <c r="C55">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56">
@@ -1014,10 +1014,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>சரவணா மெடிக்கல்ஸ்</v>
+        <v>சிவகுரு</v>
       </c>
       <c r="C56">
-        <v>500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="57">
@@ -1025,10 +1025,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>சிவகுரு</v>
+        <v>காமராஜ் வாத்தியார்</v>
       </c>
       <c r="C57">
-        <v>5000</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="58">
@@ -1036,10 +1036,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>காமராஜ் வாத்தியார்</v>
+        <v>கிருஷ்ணமூர்த்தி பழனியப்பன்</v>
       </c>
       <c r="C58">
-        <v>5001</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="59">
@@ -1047,10 +1047,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>கிருஷ்ணமூர்த்தி பழனியப்பன்</v>
+        <v>தர்மநாதன் குடும்பத்தார்கள்</v>
       </c>
       <c r="C59">
-        <v>5000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="60">
@@ -1058,10 +1058,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>தர்மநாதன் குடும்பத்தார்கள்</v>
+        <v>ராயல் தாத்தா , கலா முசிறி</v>
       </c>
       <c r="C60">
-        <v>30000</v>
+        <v>15550</v>
       </c>
     </row>
     <row r="61">
@@ -1069,10 +1069,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>ராயல் தாத்தா , கலா முசிறி</v>
+        <v>G. சரண்யா குகநாதன்</v>
       </c>
       <c r="C61">
-        <v>15550</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="62">
@@ -1080,10 +1080,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>G. சரண்யா குகநாதன்</v>
+        <v>மனோஜ்குமார் J</v>
       </c>
       <c r="C62">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="63">
@@ -1091,10 +1091,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>மனோஜ்குமார் J</v>
+        <v>பிரியா கரூர்</v>
       </c>
       <c r="C63">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="64">
@@ -1102,10 +1102,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>பிரியா கரூர்</v>
+        <v>குணா (கணேசன் )</v>
       </c>
       <c r="C64">
-        <v>1001</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="65">
@@ -1113,10 +1113,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>குணா (கணேசன் )</v>
+        <v>பாஸ்கரன் ஓட்டுனர்</v>
       </c>
       <c r="C65">
-        <v>5000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="66">
@@ -1124,10 +1124,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>பாஸ்கரன் ஓட்டுனர்</v>
+        <v>செந்தில் (தங்கராசு)</v>
       </c>
       <c r="C66">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="67">
@@ -1135,10 +1135,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>செந்தில் (தங்கராசு)</v>
+        <v>திவாகர் டிரைவர்  (வேலு)</v>
       </c>
       <c r="C67">
-        <v>5000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="68">
@@ -1146,7 +1146,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>திவாகர் டிரைவர்  (வேலு)</v>
+        <v>கார்த்திக் கரூர் (சாந்தா )</v>
       </c>
       <c r="C68">
         <v>7000</v>
@@ -1157,10 +1157,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>கார்த்திக் கரூர் (சாந்தா )</v>
+        <v>காஞ்சனா அக்கா கரூர்</v>
       </c>
       <c r="C69">
-        <v>7000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="70">
@@ -1168,10 +1168,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>காஞ்சனா அக்கா கரூர்</v>
+        <v>சுரேஷ் (பட்டு)</v>
       </c>
       <c r="C70">
-        <v>2000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71">
@@ -1179,10 +1179,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>சுரேஷ் (பட்டு)</v>
+        <v>சிவகாமி (கண்ணன்)</v>
       </c>
       <c r="C71">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72">
@@ -1190,10 +1190,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>சிவகாமி (கண்ணன்)</v>
+        <v>சுப்பிரமணி (மயில்)</v>
       </c>
       <c r="C72">
-        <v>50</v>
+        <v>500</v>
       </c>
     </row>
     <row r="73">
@@ -1201,7 +1201,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>சுப்பிரமணி (மயில்)</v>
+        <v>ராமமூர்த்தி போஸ்டல்</v>
       </c>
       <c r="C73">
         <v>500</v>
@@ -1212,10 +1212,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>ராமமூர்த்தி போஸ்டல்</v>
+        <v>மருதை வாத்தியார்</v>
       </c>
       <c r="C74">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="75">
@@ -1223,10 +1223,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>மருதை வாத்தியார்</v>
+        <v>சந்திரமோகன்</v>
       </c>
       <c r="C75">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="76">
@@ -1234,10 +1234,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>சந்திரமோகன்</v>
+        <v>தங்கவேல் (சஞ்சய்)</v>
       </c>
       <c r="C76">
-        <v>3000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77">
@@ -1245,10 +1245,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>தங்கவேல் (சஞ்சய்)</v>
+        <v>சங்கர் (முதலியார்)</v>
       </c>
       <c r="C77">
-        <v>200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="78">
@@ -1256,10 +1256,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>சங்கர் (முதலியார்)</v>
+        <v>பிச்சைமுத்து</v>
       </c>
       <c r="C78">
-        <v>1001</v>
+        <v>600</v>
       </c>
     </row>
     <row r="79">
@@ -1267,10 +1267,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>பிச்சைமுத்து</v>
+        <v>மேஸ்திரி கணேஷ்</v>
       </c>
       <c r="C79">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80">
@@ -1278,10 +1278,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>மேஸ்திரி கணேஷ்</v>
+        <v>சந்ஜீவுகுமார்</v>
       </c>
       <c r="C80">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="81">
@@ -1289,10 +1289,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>சந்ஜீவுகுமார்</v>
+        <v>புனியமூர்த்தி</v>
       </c>
       <c r="C81">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82">
@@ -1300,7 +1300,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>புனியமூர்த்தி</v>
+        <v>பேபி</v>
       </c>
       <c r="C82">
         <v>100</v>
@@ -1311,10 +1311,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>பேபி</v>
+        <v>லோகநாதன் காத்தமுத்து</v>
       </c>
       <c r="C83">
-        <v>100</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="84">
@@ -1322,10 +1322,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>லோகநாதன் காத்தமுத்து</v>
+        <v>சிவன் பக்தர்கள் SRS</v>
       </c>
       <c r="C84">
-        <v>2026</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="85">
@@ -1333,10 +1333,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>சிவன் பக்தர்கள் SRS</v>
+        <v>விக்னேஷ் ஜெகநாதன்</v>
       </c>
       <c r="C85">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="86">
@@ -1344,10 +1344,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>விக்னேஷ் ஜெகநாதன்</v>
+        <v>அருண் அன்பானந்தன்</v>
       </c>
       <c r="C86">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="87">
@@ -1355,10 +1355,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>அருண் அன்பானந்தன்</v>
+        <v>செல்லதுரை சுலோச்சனா</v>
       </c>
       <c r="C87">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="88">
@@ -1366,10 +1366,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>செல்லதுரை சுலோச்சனா</v>
+        <v>லட்சுமி ராஹவன் தொட்டியம்</v>
       </c>
       <c r="C88">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="89">
@@ -1377,10 +1377,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>லட்சுமி ராஹவன் தொட்டியம்</v>
+        <v>சதீஷ் கருக்கமடை</v>
       </c>
       <c r="C89">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="90">
@@ -1388,10 +1388,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>சதீஷ் கருக்கமடை</v>
+        <v>சாந்தி ராஜாங்கம் திம்மச்சிபுரம்</v>
       </c>
       <c r="C90">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="91">
@@ -1399,10 +1399,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="str">
-        <v>சாந்தி ராஜாங்கம் திம்மச்சிபுரம்</v>
+        <v>MI செல் ஷோரூம் தொட்டியம்</v>
       </c>
       <c r="C91">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="92">
@@ -1410,10 +1410,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="str">
-        <v>MI செல் ஷோரூம் தொட்டியம்</v>
+        <v>உதயகுமார்</v>
       </c>
       <c r="C92">
-        <v>1000</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="93">
@@ -1421,10 +1421,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="str">
-        <v>உதயகுமார்</v>
+        <v>விவேக்</v>
       </c>
       <c r="C93">
-        <v>1010</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="94">
@@ -1432,10 +1432,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="str">
-        <v>விவேக்</v>
+        <v>பாலமுருகன்(MILK)</v>
       </c>
       <c r="C94">
-        <v>3000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="95">
@@ -1443,10 +1443,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="str">
-        <v>பாலமுருகன்(MILK)</v>
+        <v>பூமதி புது தெரு</v>
       </c>
       <c r="C95">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="96">
@@ -1454,10 +1454,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="str">
-        <v>பூமதி புது தெரு</v>
+        <v>அருண் (WATRE CAN)</v>
       </c>
       <c r="C96">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97">
@@ -1465,10 +1465,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="str">
-        <v>அருண் (WATRE CAN)</v>
+        <v>போஸ்டல் சுப்பிரமணி</v>
       </c>
       <c r="C97">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="98">
@@ -1476,10 +1476,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="str">
-        <v>போஸ்டல் சுப்பிரமணி</v>
+        <v>நல்லுசாமி</v>
       </c>
       <c r="C98">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="99">
@@ -1487,10 +1487,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="str">
-        <v>நல்லுசாமி</v>
+        <v>கல்பனா கரூர்</v>
       </c>
       <c r="C99">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="100">
@@ -1498,10 +1498,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="str">
-        <v>கல்பனா கரூர்</v>
+        <v>கோபால்</v>
       </c>
       <c r="C100">
-        <v>5000</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="101">
@@ -1509,10 +1509,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="str">
-        <v>கோபால்</v>
+        <v>போஸ்டல் பெரியசாமி கரூர்</v>
       </c>
       <c r="C101">
-        <v>10001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="102">
@@ -1520,10 +1520,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="str">
-        <v>போஸ்டல் பெரியசாமி கரூர்</v>
+        <v>பானு(பூபதி)</v>
       </c>
       <c r="C102">
-        <v>5001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="103">
@@ -1531,7 +1531,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="str">
-        <v>பானு(பூபதி)</v>
+        <v>வள்ளி(பூபதி)</v>
       </c>
       <c r="C103">
         <v>2000</v>
@@ -1542,10 +1542,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="str">
-        <v>வள்ளி(பூபதி)</v>
+        <v>லதா(பழனியப்பன்)</v>
       </c>
       <c r="C104">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="105">
@@ -1553,10 +1553,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="str">
-        <v>லதா(பழனியப்பன்)</v>
+        <v>ஜீவா(திருமூர்த்தி)</v>
       </c>
       <c r="C105">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="106">
@@ -1564,10 +1564,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="str">
-        <v>ஜீவா(திருமூர்த்தி)</v>
+        <v>வினோத்(ELECTRITION)</v>
       </c>
       <c r="C106">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="107">
@@ -1575,10 +1575,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="str">
-        <v>வினோத்(ELECTRITION)</v>
+        <v>கருணாநிதி மளிகை</v>
       </c>
       <c r="C107">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="108">
@@ -1586,10 +1586,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="str">
-        <v>கருணாநிதி மளிகை</v>
+        <v>லதா பழனியப்பன்</v>
       </c>
       <c r="C108">
-        <v>1000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="109">
@@ -1597,10 +1597,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="str">
-        <v>லதா பழனியப்பன்</v>
+        <v>மலர்கொடி</v>
       </c>
       <c r="C109">
-        <v>2001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="110">
@@ -1608,10 +1608,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="str">
-        <v>மலர்கொடி</v>
+        <v>சுமன் காவேரி நகர்</v>
       </c>
       <c r="C110">
-        <v>1000</v>
+        <v>501</v>
       </c>
     </row>
     <row r="111">
@@ -1619,10 +1619,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="str">
-        <v>சுமன் காவேரி நகர்</v>
+        <v>நக்கராஜ் இலை வியாபாரம்</v>
       </c>
       <c r="C111">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="112">
@@ -1630,10 +1630,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="str">
-        <v>நக்கராஜ் இலை வியாபாரம்</v>
+        <v>ஆசாரி செல்வம்</v>
       </c>
       <c r="C112">
-        <v>500</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="113">
@@ -1641,10 +1641,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="str">
-        <v>ஆசாரி செல்வம்</v>
+        <v>லோகநாதன் சுப்ரமணியன்</v>
       </c>
       <c r="C113">
-        <v>1005</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="114">
@@ -1652,10 +1652,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="str">
-        <v>லோகநாதன் சுப்ரமணியன்</v>
+        <v>சுதாகர் ஆர்மி</v>
       </c>
       <c r="C114">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="115">
@@ -1663,10 +1663,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="str">
-        <v>சுதாகர் ஆர்மி</v>
+        <v>சின்னசாமி ஊஞ்சி</v>
       </c>
       <c r="C115">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="116">
@@ -1674,10 +1674,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="str">
-        <v>சின்னசாமி ஊஞ்சி</v>
+        <v>ராஜா சார் SRS</v>
       </c>
       <c r="C116">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="117">
@@ -1685,10 +1685,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="str">
-        <v>ராஜா சார் SRS</v>
+        <v>மாரியாயி ஆனடபுரம் குடும்பத்தார்</v>
       </c>
       <c r="C117">
-        <v>2000</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="118">
@@ -1696,10 +1696,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="str">
-        <v>மாரியாயி ஆனடபுரம் குடும்பத்தார்</v>
+        <v>பாலமுருகன் புடலாத்ததி</v>
       </c>
       <c r="C118">
-        <v>11001</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="119">
@@ -1707,10 +1707,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="str">
-        <v>பாலமுருகன் புடலாத்ததி</v>
+        <v>கணேசன் செம்பன்</v>
       </c>
       <c r="C119">
-        <v>10000</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="120">
@@ -1718,10 +1718,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="str">
-        <v>கணேசன் செம்பன்</v>
+        <v>ஜோதிமணி</v>
       </c>
       <c r="C120">
-        <v>5010</v>
+        <v>200</v>
       </c>
     </row>
     <row r="121">
@@ -1729,10 +1729,10 @@
         <v>120</v>
       </c>
       <c r="B121" t="str">
-        <v>ஜோதிமணி</v>
+        <v>குணசேகரன் சித்திரா</v>
       </c>
       <c r="C121">
-        <v>200</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="122">
@@ -1740,10 +1740,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="str">
-        <v>குணசேகரன் சித்திரா</v>
+        <v>தங்கராஜ்</v>
       </c>
       <c r="C122">
-        <v>4001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="123">
@@ -1751,7 +1751,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="str">
-        <v>தங்கராஜ்</v>
+        <v>ரெங்கநாதன்</v>
       </c>
       <c r="C123">
         <v>1000</v>
@@ -1762,7 +1762,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="str">
-        <v>ரெங்கநாதன்</v>
+        <v>ஜெயராஜ்</v>
       </c>
       <c r="C124">
         <v>1000</v>
@@ -1773,7 +1773,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="str">
-        <v>ஜெயராஜ்</v>
+        <v>சரோஜா</v>
       </c>
       <c r="C125">
         <v>1000</v>
@@ -1784,7 +1784,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="str">
-        <v>சரோஜா</v>
+        <v>சுரேஷ் காத்தான்</v>
       </c>
       <c r="C126">
         <v>1000</v>
@@ -1795,10 +1795,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="str">
-        <v>சுரேஷ் காத்தான்</v>
+        <v>மாரியப்பன்</v>
       </c>
       <c r="C127">
-        <v>1000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="128">
@@ -1806,10 +1806,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="str">
-        <v>மாரியப்பன்</v>
+        <v>செல்வம் A1</v>
       </c>
       <c r="C128">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="129">
@@ -1817,10 +1817,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="str">
-        <v>செல்வம் A1</v>
+        <v>தியாகராஜன் சலூன்</v>
       </c>
       <c r="C129">
-        <v>500</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="130">
@@ -1828,10 +1828,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="str">
-        <v>தியாகராஜன் சலூன்</v>
+        <v>சிவகுமார்</v>
       </c>
       <c r="C130">
-        <v>1101</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="131">
@@ -1839,10 +1839,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="str">
-        <v>சிவகுமார்</v>
+        <v>சந்திரன்</v>
       </c>
       <c r="C131">
-        <v>1000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="132">
@@ -1850,10 +1850,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="str">
-        <v>சந்திரன்</v>
+        <v>கும்பாபிசேகம் நாள் நன்கொடை வரவு</v>
       </c>
       <c r="C132">
-        <v>200</v>
+        <v>37688</v>
       </c>
     </row>
     <row r="133">
@@ -1861,10 +1861,10 @@
         <v>132</v>
       </c>
       <c r="B133" t="str">
-        <v>கும்பாபிசேகம் நாள் நன்கொடை வரவு</v>
+        <v>Demo User</v>
       </c>
       <c r="C133">
-        <v>37688</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="134">
@@ -1883,26 +1883,15 @@
         <v>134</v>
       </c>
       <c r="B135" t="str">
-        <v>Demo User</v>
+        <v>testuser</v>
       </c>
       <c r="C135">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136">
-        <v>135</v>
-      </c>
-      <c r="B136" t="str">
-        <v>testuser</v>
-      </c>
-      <c r="C136">
         <v>1332</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C136"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C135"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:C134"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -420,10 +420,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>ஸ்ரீனிவாச அய்யர்</v>
+        <v>லட்சுமி</v>
       </c>
       <c r="C2">
-        <v>10001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="3">
@@ -431,10 +431,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>லட்சுமி</v>
+        <v>செந்தில் (சக்கரவர்த்தி)</v>
       </c>
       <c r="C3">
-        <v>5001</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="4">
@@ -442,10 +442,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>செந்தில் (சக்கரவர்த்தி)</v>
+        <v>ஆனந்த்</v>
       </c>
       <c r="C4">
-        <v>4700</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="5">
@@ -453,7 +453,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>ஆனந்த்</v>
+        <v>யோகேஷ்</v>
       </c>
       <c r="C5">
         <v>19000</v>
@@ -464,10 +464,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>யோகேஷ்</v>
+        <v>சுரேஷ்</v>
       </c>
       <c r="C6">
-        <v>19000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="7">
@@ -475,10 +475,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>சுரேஷ்</v>
+        <v>பூபதி</v>
       </c>
       <c r="C7">
-        <v>20000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>பூபதி</v>
+        <v>நந்தகுமார்</v>
       </c>
       <c r="C8">
-        <v>27500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="9">
@@ -497,10 +497,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>நந்தகுமார்</v>
+        <v>ரமேஷ்(டிரைவர்)</v>
       </c>
       <c r="C9">
-        <v>9500</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -508,10 +508,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>ரமேஷ்(டிரைவர்)</v>
+        <v>கண்ணன்(post)</v>
       </c>
       <c r="C10">
-        <v>101</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="11">
@@ -519,10 +519,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>கண்ணன்(post)</v>
+        <v>ரமேஷ்(PC)</v>
       </c>
       <c r="C11">
-        <v>10001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
@@ -530,10 +530,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>ரமேஷ்(PC)</v>
+        <v>வெற்றிவேல்</v>
       </c>
       <c r="C12">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="13">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>வெற்றிவேல்</v>
+        <v>ஏ. தினேஷ்குமார்</v>
       </c>
       <c r="C13">
         <v>3000</v>
@@ -552,10 +552,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>ஏ. தினேஷ்குமார்</v>
+        <v>சூர்யா கார்த்தி (சீலைபில்லையர்புதூர்)</v>
       </c>
       <c r="C14">
-        <v>3000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="15">
@@ -563,10 +563,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>சூர்யா கார்த்தி (சீலைபில்லையர்புதூர்)</v>
+        <v>சுஜிதா ஈரோடு</v>
       </c>
       <c r="C15">
-        <v>12000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="16">
@@ -574,10 +574,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>சுஜிதா ஈரோடு</v>
+        <v>நாகராஜ் அய்யர்</v>
       </c>
       <c r="C16">
-        <v>2000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17">
@@ -585,10 +585,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>நாகராஜ் அய்யர்</v>
+        <v>நட்ராஜ் கோவை (மணி)</v>
       </c>
       <c r="C17">
-        <v>500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="18">
@@ -596,10 +596,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>நட்ராஜ் கோவை (மணி)</v>
+        <v>தனலட்சுமி புகழேந்தி</v>
       </c>
       <c r="C18">
-        <v>5500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19">
@@ -607,10 +607,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>தனலட்சுமி புகழேந்தி</v>
+        <v>ராஜசேகர் பழனியப்பன்</v>
       </c>
       <c r="C19">
-        <v>500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="20">
@@ -618,10 +618,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>ராஜசேகர் பழனியப்பன்</v>
+        <v>நடராஜன் சைக்கிள்</v>
       </c>
       <c r="C20">
-        <v>10000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="21">
@@ -629,10 +629,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>நடராஜன் சைக்கிள்</v>
+        <v>எவுரி (postal)</v>
       </c>
       <c r="C21">
-        <v>1000</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="22">
@@ -640,10 +640,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>எவுரி (postal)</v>
+        <v>அருண் இரத்த பரிசோதனை (காட்டுபுத்தூர்)</v>
       </c>
       <c r="C22">
-        <v>5001</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>அருண் இரத்த பரிசோதனை (காட்டுபுத்தூர்)</v>
+        <v>ராஜேந்திரன் சுப்ரமணி</v>
       </c>
       <c r="C23">
-        <v>15000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="24">
@@ -662,10 +662,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>ராஜேந்திரன் சுப்ரமணி</v>
+        <v>சந்தோஸ் ரமேஷ்</v>
       </c>
       <c r="C24">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="25">
@@ -673,10 +673,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>சந்தோஸ் ரமேஷ்</v>
+        <v>ரமேஷ் பன்னீர்செல்வம்</v>
       </c>
       <c r="C25">
-        <v>10000</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="26">
@@ -684,10 +684,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>ரமேஷ் பன்னீர்செல்வம்</v>
+        <v>முத்துகிருஷ்ணன்</v>
       </c>
       <c r="C26">
-        <v>10001</v>
+        <v>5501</v>
       </c>
     </row>
     <row r="27">
@@ -695,10 +695,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>முத்துகிருஷ்ணன்</v>
+        <v>சுபாஷினி காட்டுப்புத்தூர்</v>
       </c>
       <c r="C27">
-        <v>5501</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="28">
@@ -706,10 +706,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>சுபாஷினி காட்டுப்புத்தூர்</v>
+        <v>அமுதா அன்பாநந்தன்</v>
       </c>
       <c r="C28">
-        <v>1000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="29">
@@ -717,10 +717,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>அமுதா அன்பாநந்தன்</v>
+        <v>கமல்நாத் கொளக்குடி</v>
       </c>
       <c r="C29">
-        <v>12500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30">
@@ -728,10 +728,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>கமல்நாத் கொளக்குடி</v>
+        <v>ஸ்ரீனிவாசபிரபு</v>
       </c>
       <c r="C30">
-        <v>300</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="31">
@@ -739,10 +739,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>ஸ்ரீனிவாசபிரபு</v>
+        <v>நாகவேல்</v>
       </c>
       <c r="C31">
-        <v>5001</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="32">
@@ -750,10 +750,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>நாகவேல்</v>
+        <v>செல்வராஜ் (TNEB)</v>
       </c>
       <c r="C32">
-        <v>17500</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="33">
@@ -761,7 +761,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>செல்வராஜ் (TNEB)</v>
+        <v>சதிஸ்குமார் (VAO)</v>
       </c>
       <c r="C33">
         <v>10001</v>
@@ -772,10 +772,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>சதிஸ்குமார் (VAO)</v>
+        <v>சரவணன் சதாசிவம்</v>
       </c>
       <c r="C34">
-        <v>10001</v>
+        <v>10501</v>
       </c>
     </row>
     <row r="35">
@@ -783,10 +783,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>சரவணன் சதாசிவம்</v>
+        <v>பிரியா நரேந்தரகுமார்</v>
       </c>
       <c r="C35">
-        <v>10501</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="36">
@@ -794,10 +794,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>பிரியா நரேந்தரகுமார்</v>
+        <v>புகழேந்தி டைலர்</v>
       </c>
       <c r="C36">
-        <v>1001</v>
+        <v>700</v>
       </c>
     </row>
     <row r="37">
@@ -805,10 +805,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>புகழேந்தி டைலர்</v>
+        <v>தங்கராசு கிருஷ்ணன்</v>
       </c>
       <c r="C37">
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="38">
@@ -816,10 +816,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>தங்கராசு கிருஷ்ணன்</v>
+        <v>சரவணன் ராஜசுந்தரி (தொட்டியம்)</v>
       </c>
       <c r="C38">
-        <v>2000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="39">
@@ -827,10 +827,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>சரவணன் ராஜசுந்தரி (தொட்டியம்)</v>
+        <v>ரெங்கநாதன் ரைஸ் மில்</v>
       </c>
       <c r="C39">
-        <v>10000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="40">
@@ -838,10 +838,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>ரெங்கநாதன் ரைஸ் மில்</v>
+        <v>வினோத் நீலமேகம்</v>
       </c>
       <c r="C40">
-        <v>25000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="41">
@@ -849,10 +849,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>வினோத் நீலமேகம்</v>
+        <v>சூர்யகுமார்</v>
       </c>
       <c r="C41">
-        <v>1000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="42">
@@ -860,10 +860,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>சூர்யகுமார்</v>
+        <v>சிவஞானம் ரெத்தினவேல்</v>
       </c>
       <c r="C42">
-        <v>2500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="43">
@@ -871,7 +871,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>சிவஞானம் ரெத்தினவேல்</v>
+        <v>நடராஜன் வாத்தியார்</v>
       </c>
       <c r="C43">
         <v>5000</v>
@@ -882,10 +882,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>நடராஜன் வாத்தியார்</v>
+        <v>பொங்கல் விளையாட்டு பணம்</v>
       </c>
       <c r="C44">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="45">
@@ -893,10 +893,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>பொங்கல் விளையாட்டு பணம்</v>
+        <v>அஜீத்குமார்சென்னை</v>
       </c>
       <c r="C45">
-        <v>6000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="46">
@@ -904,10 +904,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>அஜீத்குமார்சென்னை</v>
+        <v>ரவி மணி</v>
       </c>
       <c r="C46">
-        <v>500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="47">
@@ -915,10 +915,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>ரவி மணி</v>
+        <v>வீமன்</v>
       </c>
       <c r="C47">
-        <v>10000</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="48">
@@ -926,10 +926,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>வீமன்</v>
+        <v>குருசாமி (புது தெரு)</v>
       </c>
       <c r="C48">
-        <v>5001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="49">
@@ -937,10 +937,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>குருசாமி (புது தெரு)</v>
+        <v>ராஜு மரகதம்</v>
       </c>
       <c r="C49">
-        <v>2000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="50">
@@ -948,10 +948,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>ராஜு மரகதம்</v>
+        <v>H திருமூர்த்தி</v>
       </c>
       <c r="C50">
-        <v>15000</v>
+        <v>5111</v>
       </c>
     </row>
     <row r="51">
@@ -959,10 +959,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>H திருமூர்த்தி</v>
+        <v>Dr. மோகன்</v>
       </c>
       <c r="C51">
-        <v>5111</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="52">
@@ -970,10 +970,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>Dr. மோகன்</v>
+        <v>அதிபன் (மதி டிஃபன்)</v>
       </c>
       <c r="C52">
-        <v>20000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="53">
@@ -981,10 +981,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>அதிபன் (மதி டிஃபன்)</v>
+        <v>நாகப்பா ஜவுளி</v>
       </c>
       <c r="C53">
-        <v>1000</v>
+        <v>501</v>
       </c>
     </row>
     <row r="54">
@@ -992,10 +992,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>நாகப்பா ஜவுளி</v>
+        <v>சரவணா மெடிக்கல்ஸ்</v>
       </c>
       <c r="C54">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="55">
@@ -1003,10 +1003,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>சரவணா மெடிக்கல்ஸ்</v>
+        <v>சிவகுரு</v>
       </c>
       <c r="C55">
-        <v>500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="56">
@@ -1014,10 +1014,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>சிவகுரு</v>
+        <v>காமராஜ் வாத்தியார்</v>
       </c>
       <c r="C56">
-        <v>5000</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="57">
@@ -1025,10 +1025,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>காமராஜ் வாத்தியார்</v>
+        <v>கிருஷ்ணமூர்த்தி பழனியப்பன்</v>
       </c>
       <c r="C57">
-        <v>5001</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="58">
@@ -1036,10 +1036,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>கிருஷ்ணமூர்த்தி பழனியப்பன்</v>
+        <v>தர்மநாதன் குடும்பத்தார்கள்</v>
       </c>
       <c r="C58">
-        <v>5000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="59">
@@ -1047,10 +1047,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>தர்மநாதன் குடும்பத்தார்கள்</v>
+        <v>ராயல் தாத்தா , கலா முசிறி</v>
       </c>
       <c r="C59">
-        <v>30000</v>
+        <v>15550</v>
       </c>
     </row>
     <row r="60">
@@ -1058,10 +1058,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>ராயல் தாத்தா , கலா முசிறி</v>
+        <v>G. சரண்யா குகநாதன்</v>
       </c>
       <c r="C60">
-        <v>15550</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="61">
@@ -1069,10 +1069,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>G. சரண்யா குகநாதன்</v>
+        <v>மனோஜ்குமார் J</v>
       </c>
       <c r="C61">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="62">
@@ -1080,10 +1080,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>மனோஜ்குமார் J</v>
+        <v>பிரியா கரூர்</v>
       </c>
       <c r="C62">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="63">
@@ -1091,10 +1091,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>பிரியா கரூர்</v>
+        <v>குணா (கணேசன் )</v>
       </c>
       <c r="C63">
-        <v>1001</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="64">
@@ -1102,10 +1102,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>குணா (கணேசன் )</v>
+        <v>பாஸ்கரன் ஓட்டுனர்</v>
       </c>
       <c r="C64">
-        <v>5000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="65">
@@ -1113,10 +1113,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>பாஸ்கரன் ஓட்டுனர்</v>
+        <v>செந்தில் (தங்கராசு)</v>
       </c>
       <c r="C65">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="66">
@@ -1124,10 +1124,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>செந்தில் (தங்கராசு)</v>
+        <v>திவாகர் டிரைவர்  (வேலு)</v>
       </c>
       <c r="C66">
-        <v>5000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="67">
@@ -1135,7 +1135,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>திவாகர் டிரைவர்  (வேலு)</v>
+        <v>கார்த்திக் கரூர் (சாந்தா )</v>
       </c>
       <c r="C67">
         <v>7000</v>
@@ -1146,10 +1146,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>கார்த்திக் கரூர் (சாந்தா )</v>
+        <v>காஞ்சனா அக்கா கரூர்</v>
       </c>
       <c r="C68">
-        <v>7000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="69">
@@ -1157,10 +1157,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>காஞ்சனா அக்கா கரூர்</v>
+        <v>சுரேஷ் (பட்டு)</v>
       </c>
       <c r="C69">
-        <v>2000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70">
@@ -1168,10 +1168,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>சுரேஷ் (பட்டு)</v>
+        <v>சிவகாமி (கண்ணன்)</v>
       </c>
       <c r="C70">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71">
@@ -1179,10 +1179,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>சிவகாமி (கண்ணன்)</v>
+        <v>சுப்பிரமணி (மயில்)</v>
       </c>
       <c r="C71">
-        <v>50</v>
+        <v>500</v>
       </c>
     </row>
     <row r="72">
@@ -1190,7 +1190,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>சுப்பிரமணி (மயில்)</v>
+        <v>ராமமூர்த்தி போஸ்டல்</v>
       </c>
       <c r="C72">
         <v>500</v>
@@ -1201,10 +1201,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>ராமமூர்த்தி போஸ்டல்</v>
+        <v>மருதை வாத்தியார்</v>
       </c>
       <c r="C73">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="74">
@@ -1212,10 +1212,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>மருதை வாத்தியார்</v>
+        <v>சந்திரமோகன்</v>
       </c>
       <c r="C74">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="75">
@@ -1223,10 +1223,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>சந்திரமோகன்</v>
+        <v>தங்கவேல் (சஞ்சய்)</v>
       </c>
       <c r="C75">
-        <v>3000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="76">
@@ -1234,10 +1234,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>தங்கவேல் (சஞ்சய்)</v>
+        <v>சங்கர் (முதலியார்)</v>
       </c>
       <c r="C76">
-        <v>200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="77">
@@ -1245,10 +1245,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>சங்கர் (முதலியார்)</v>
+        <v>பிச்சைமுத்து</v>
       </c>
       <c r="C77">
-        <v>1001</v>
+        <v>600</v>
       </c>
     </row>
     <row r="78">
@@ -1256,10 +1256,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>பிச்சைமுத்து</v>
+        <v>மேஸ்திரி கணேஷ்</v>
       </c>
       <c r="C78">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79">
@@ -1267,10 +1267,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>மேஸ்திரி கணேஷ்</v>
+        <v>சந்ஜீவுகுமார்</v>
       </c>
       <c r="C79">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80">
@@ -1278,10 +1278,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>சந்ஜீவுகுமார்</v>
+        <v>புனியமூர்த்தி</v>
       </c>
       <c r="C80">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81">
@@ -1289,7 +1289,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>புனியமூர்த்தி</v>
+        <v>பேபி</v>
       </c>
       <c r="C81">
         <v>100</v>
@@ -1300,10 +1300,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>பேபி</v>
+        <v>லோகநாதன் காத்தமுத்து</v>
       </c>
       <c r="C82">
-        <v>100</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="83">
@@ -1311,10 +1311,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>லோகநாதன் காத்தமுத்து</v>
+        <v>சிவன் பக்தர்கள் SRS</v>
       </c>
       <c r="C83">
-        <v>2026</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="84">
@@ -1322,10 +1322,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>சிவன் பக்தர்கள் SRS</v>
+        <v>விக்னேஷ் ஜெகநாதன்</v>
       </c>
       <c r="C84">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="85">
@@ -1333,10 +1333,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>விக்னேஷ் ஜெகநாதன்</v>
+        <v>அருண் அன்பானந்தன்</v>
       </c>
       <c r="C85">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="86">
@@ -1344,10 +1344,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>அருண் அன்பானந்தன்</v>
+        <v>செல்லதுரை சுலோச்சனா</v>
       </c>
       <c r="C86">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="87">
@@ -1355,10 +1355,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>செல்லதுரை சுலோச்சனா</v>
+        <v>லட்சுமி ராஹவன் தொட்டியம்</v>
       </c>
       <c r="C87">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="88">
@@ -1366,10 +1366,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>லட்சுமி ராஹவன் தொட்டியம்</v>
+        <v>சதீஷ் கருக்கமடை</v>
       </c>
       <c r="C88">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89">
@@ -1377,10 +1377,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>சதீஷ் கருக்கமடை</v>
+        <v>சாந்தி ராஜாங்கம் திம்மச்சிபுரம்</v>
       </c>
       <c r="C89">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="90">
@@ -1388,10 +1388,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>சாந்தி ராஜாங்கம் திம்மச்சிபுரம்</v>
+        <v>MI செல் ஷோரூம் தொட்டியம்</v>
       </c>
       <c r="C90">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="91">
@@ -1399,10 +1399,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="str">
-        <v>MI செல் ஷோரூம் தொட்டியம்</v>
+        <v>உதயகுமார்</v>
       </c>
       <c r="C91">
-        <v>1000</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="92">
@@ -1410,10 +1410,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="str">
-        <v>உதயகுமார்</v>
+        <v>விவேக்</v>
       </c>
       <c r="C92">
-        <v>1010</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="93">
@@ -1421,10 +1421,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="str">
-        <v>விவேக்</v>
+        <v>பாலமுருகன்(MILK)</v>
       </c>
       <c r="C93">
-        <v>3000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="94">
@@ -1432,10 +1432,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="str">
-        <v>பாலமுருகன்(MILK)</v>
+        <v>பூமதி புது தெரு</v>
       </c>
       <c r="C94">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="95">
@@ -1443,10 +1443,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="str">
-        <v>பூமதி புது தெரு</v>
+        <v>அருண் (WATRE CAN)</v>
       </c>
       <c r="C95">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96">
@@ -1454,10 +1454,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="str">
-        <v>அருண் (WATRE CAN)</v>
+        <v>போஸ்டல் சுப்பிரமணி</v>
       </c>
       <c r="C96">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="97">
@@ -1465,10 +1465,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="str">
-        <v>போஸ்டல் சுப்பிரமணி</v>
+        <v>நல்லுசாமி</v>
       </c>
       <c r="C97">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="98">
@@ -1476,10 +1476,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="str">
-        <v>நல்லுசாமி</v>
+        <v>கல்பனா கரூர்</v>
       </c>
       <c r="C98">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="99">
@@ -1487,10 +1487,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="str">
-        <v>கல்பனா கரூர்</v>
+        <v>கோபால்</v>
       </c>
       <c r="C99">
-        <v>5000</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="100">
@@ -1498,10 +1498,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="str">
-        <v>கோபால்</v>
+        <v>போஸ்டல் பெரியசாமி கரூர்</v>
       </c>
       <c r="C100">
-        <v>10001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="101">
@@ -1509,10 +1509,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="str">
-        <v>போஸ்டல் பெரியசாமி கரூர்</v>
+        <v>பானு(பூபதி)</v>
       </c>
       <c r="C101">
-        <v>5001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="102">
@@ -1520,7 +1520,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="str">
-        <v>பானு(பூபதி)</v>
+        <v>வள்ளி(பூபதி)</v>
       </c>
       <c r="C102">
         <v>2000</v>
@@ -1531,10 +1531,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="str">
-        <v>வள்ளி(பூபதி)</v>
+        <v>லதா(பழனியப்பன்)</v>
       </c>
       <c r="C103">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="104">
@@ -1542,10 +1542,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="str">
-        <v>லதா(பழனியப்பன்)</v>
+        <v>ஜீவா(திருமூர்த்தி)</v>
       </c>
       <c r="C104">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="105">
@@ -1553,10 +1553,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="str">
-        <v>ஜீவா(திருமூர்த்தி)</v>
+        <v>வினோத்(ELECTRITION)</v>
       </c>
       <c r="C105">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="106">
@@ -1564,10 +1564,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="str">
-        <v>வினோத்(ELECTRITION)</v>
+        <v>கருணாநிதி மளிகை</v>
       </c>
       <c r="C106">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="107">
@@ -1575,10 +1575,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="str">
-        <v>கருணாநிதி மளிகை</v>
+        <v>லதா பழனியப்பன்</v>
       </c>
       <c r="C107">
-        <v>1000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="108">
@@ -1586,10 +1586,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="str">
-        <v>லதா பழனியப்பன்</v>
+        <v>மலர்கொடி</v>
       </c>
       <c r="C108">
-        <v>2001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="109">
@@ -1597,10 +1597,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="str">
-        <v>மலர்கொடி</v>
+        <v>சுமன் காவேரி நகர்</v>
       </c>
       <c r="C109">
-        <v>1000</v>
+        <v>501</v>
       </c>
     </row>
     <row r="110">
@@ -1608,10 +1608,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="str">
-        <v>சுமன் காவேரி நகர்</v>
+        <v>நக்கராஜ் இலை வியாபாரம்</v>
       </c>
       <c r="C110">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="111">
@@ -1619,10 +1619,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="str">
-        <v>நக்கராஜ் இலை வியாபாரம்</v>
+        <v>ஆசாரி செல்வம்</v>
       </c>
       <c r="C111">
-        <v>500</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="112">
@@ -1630,10 +1630,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="str">
-        <v>ஆசாரி செல்வம்</v>
+        <v>லோகநாதன் சுப்ரமணியன்</v>
       </c>
       <c r="C112">
-        <v>1005</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="113">
@@ -1641,10 +1641,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="str">
-        <v>லோகநாதன் சுப்ரமணியன்</v>
+        <v>சுதாகர் ஆர்மி</v>
       </c>
       <c r="C113">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="114">
@@ -1652,10 +1652,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="str">
-        <v>சுதாகர் ஆர்மி</v>
+        <v>சின்னசாமி ஊஞ்சி</v>
       </c>
       <c r="C114">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="115">
@@ -1663,10 +1663,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="str">
-        <v>சின்னசாமி ஊஞ்சி</v>
+        <v>ராஜா சார் SRS</v>
       </c>
       <c r="C115">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="116">
@@ -1674,10 +1674,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="str">
-        <v>ராஜா சார் SRS</v>
+        <v>மாரியாயி ஆனடபுரம் குடும்பத்தார்</v>
       </c>
       <c r="C116">
-        <v>2000</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="117">
@@ -1685,10 +1685,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="str">
-        <v>மாரியாயி ஆனடபுரம் குடும்பத்தார்</v>
+        <v>பாலமுருகன் புடலாத்ததி</v>
       </c>
       <c r="C117">
-        <v>11001</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="118">
@@ -1696,10 +1696,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="str">
-        <v>பாலமுருகன் புடலாத்ததி</v>
+        <v>கணேசன் செம்பன்</v>
       </c>
       <c r="C118">
-        <v>10000</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="119">
@@ -1707,10 +1707,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="str">
-        <v>கணேசன் செம்பன்</v>
+        <v>ஜோதிமணி</v>
       </c>
       <c r="C119">
-        <v>5010</v>
+        <v>200</v>
       </c>
     </row>
     <row r="120">
@@ -1718,10 +1718,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="str">
-        <v>ஜோதிமணி</v>
+        <v>குணசேகரன் சித்திரா</v>
       </c>
       <c r="C120">
-        <v>200</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="121">
@@ -1729,10 +1729,10 @@
         <v>120</v>
       </c>
       <c r="B121" t="str">
-        <v>குணசேகரன் சித்திரா</v>
+        <v>தங்கராஜ்</v>
       </c>
       <c r="C121">
-        <v>4001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="122">
@@ -1740,7 +1740,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="str">
-        <v>தங்கராஜ்</v>
+        <v>ரெங்கநாதன்</v>
       </c>
       <c r="C122">
         <v>1000</v>
@@ -1751,7 +1751,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="str">
-        <v>ரெங்கநாதன்</v>
+        <v>ஜெயராஜ்</v>
       </c>
       <c r="C123">
         <v>1000</v>
@@ -1762,7 +1762,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="str">
-        <v>ஜெயராஜ்</v>
+        <v>சரோஜா</v>
       </c>
       <c r="C124">
         <v>1000</v>
@@ -1773,7 +1773,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="str">
-        <v>சரோஜா</v>
+        <v>சுரேஷ் காத்தான்</v>
       </c>
       <c r="C125">
         <v>1000</v>
@@ -1784,10 +1784,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="str">
-        <v>சுரேஷ் காத்தான்</v>
+        <v>மாரியப்பன்</v>
       </c>
       <c r="C126">
-        <v>1000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="127">
@@ -1795,10 +1795,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="str">
-        <v>மாரியப்பன்</v>
+        <v>செல்வம் A1</v>
       </c>
       <c r="C127">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="128">
@@ -1806,10 +1806,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="str">
-        <v>செல்வம் A1</v>
+        <v>தியாகராஜன் சலூன்</v>
       </c>
       <c r="C128">
-        <v>500</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="129">
@@ -1817,10 +1817,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="str">
-        <v>தியாகராஜன் சலூன்</v>
+        <v>சிவகுமார்</v>
       </c>
       <c r="C129">
-        <v>1101</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="130">
@@ -1828,10 +1828,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="str">
-        <v>சிவகுமார்</v>
+        <v>சந்திரன்</v>
       </c>
       <c r="C130">
-        <v>1000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="131">
@@ -1839,10 +1839,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="str">
-        <v>சந்திரன்</v>
+        <v>கும்பாபிசேகம் நாள் நன்கொடை வரவு</v>
       </c>
       <c r="C131">
-        <v>200</v>
+        <v>37688</v>
       </c>
     </row>
     <row r="132">
@@ -1850,10 +1850,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="str">
-        <v>கும்பாபிசேகம் நாள் நன்கொடை வரவு</v>
+        <v>Demo User</v>
       </c>
       <c r="C132">
-        <v>37688</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="133">
@@ -1872,26 +1872,15 @@
         <v>133</v>
       </c>
       <c r="B134" t="str">
-        <v>Demo User</v>
+        <v>testuser</v>
       </c>
       <c r="C134">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135">
-        <v>134</v>
-      </c>
-      <c r="B135" t="str">
-        <v>testuser</v>
-      </c>
-      <c r="C135">
         <v>1332</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C135"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C134"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -420,10 +420,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>dfksddf333</v>
+        <v>பூபதி</v>
       </c>
       <c r="C2">
-        <v>4555</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -426,9 +426,20 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ஆன ஆனந்த் புகழேந்தி</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -426,20 +426,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>ஆன ஆனந்த் புகழேந்தி</v>
-      </c>
-      <c r="C3">
-        <v>1000</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -420,7 +420,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>பூபதி</v>
+        <v>பூபதி (EB)</v>
       </c>
       <c r="C2">
         <v>1000</v>

--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -426,9 +426,20 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>கோகுல் கண்ணன்</v>
+      </c>
+      <c r="C3">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -437,9 +437,20 @@
         <v>500</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>யோகேஷ்</v>
+      </c>
+      <c r="C4">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -448,9 +448,20 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>ரமேஷ் டிரைவர்</v>
+      </c>
+      <c r="C5">
+        <v>300</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -459,9 +459,20 @@
         <v>300</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>ரமேஷ் போலீஸ்</v>
+      </c>
+      <c r="C6">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -442,7 +442,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>யோகேஷ்</v>
+        <v>யோகேஷ் புகழேந்தி</v>
       </c>
       <c r="C4">
         <v>1000</v>

--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -470,9 +470,20 @@
         <v>500</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>பாலமுருகன் ரஞ்சனி</v>
+      </c>
+      <c r="C7">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -481,9 +481,20 @@
         <v>500</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>லோகு காத்தமுத்து</v>
+      </c>
+      <c r="C8">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -492,9 +492,20 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>கார்த்தி மற்றும் ரமணன் (கோபால்)</v>
+      </c>
+      <c r="C9">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -503,9 +503,20 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>விக்னேஷ் ஜெகநாதன்</v>
+      </c>
+      <c r="C10">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -514,9 +514,20 @@
         <v>500</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>ராஜேந்திரன் சுப்பிரமணியன்</v>
+      </c>
+      <c r="C11">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -525,9 +525,20 @@
         <v>500</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>ரமேஷ் பன்னீர்செல்வம்</v>
+      </c>
+      <c r="C12">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -536,9 +536,20 @@
         <v>500</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>சந்தோஷ் ரமேஷ்</v>
+      </c>
+      <c r="C13">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/donors.xlsx
+++ b/data/donors.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -547,9 +547,20 @@
         <v>500</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>சுரேஷ் பிரகாசம்</v>
+      </c>
+      <c r="C14">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
   </ignoredErrors>
 </worksheet>
 </file>